--- a/vocabulaire.xlsx
+++ b/vocabulaire.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ff63f536390cb2c5/Bureau/oulpan-quizz/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ambia\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="395" documentId="8_{FB1266D2-B91B-44BD-B92B-71C020DB630F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07DE6788-F244-41E0-B20E-5D05FE438992}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F0D310D-6DA3-473F-AF3A-3D9EF56D2887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="9" activeTab="14" xr2:uid="{70BF4402-85FA-49F6-9F7C-8C962336CB2E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{70BF4402-85FA-49F6-9F7C-8C962336CB2E}"/>
   </bookViews>
   <sheets>
     <sheet name="verbes" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3149" uniqueCount="2933">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3239" uniqueCount="3018">
   <si>
     <t>Transcription</t>
   </si>
@@ -5457,9 +5457,6 @@
     <t xml:space="preserve">מה המחיר? </t>
   </si>
   <si>
-    <t>addition</t>
-  </si>
-  <si>
     <t>חשבון</t>
   </si>
   <si>
@@ -5907,9 +5904,6 @@
     <t>tinokot</t>
   </si>
   <si>
-    <t>khechbone</t>
-  </si>
-  <si>
     <t>lo + verbe + rien</t>
   </si>
   <si>
@@ -6192,9 +6186,6 @@
     <t>toda</t>
   </si>
   <si>
-    <t>vidéo</t>
-  </si>
-  <si>
     <t>וידאו</t>
   </si>
   <si>
@@ -7413,9 +7404,6 @@
     <t>מתחילות</t>
   </si>
   <si>
-    <t>lehat’hil</t>
-  </si>
-  <si>
     <t>réussir</t>
   </si>
   <si>
@@ -7435,9 +7423,6 @@
   </si>
   <si>
     <t>stylo</t>
-  </si>
-  <si>
-    <t>lenassot</t>
   </si>
   <si>
     <t>voler (un bien)</t>
@@ -8863,6 +8848,276 @@
   </si>
   <si>
     <t>ketchoupim</t>
+  </si>
+  <si>
+    <t>s'enthousiasmer</t>
+  </si>
+  <si>
+    <t>להתרגש</t>
+  </si>
+  <si>
+    <t>se laver</t>
+  </si>
+  <si>
+    <t>להתרחץ</t>
+  </si>
+  <si>
+    <t>להתחתן</t>
+  </si>
+  <si>
+    <t>se marier</t>
+  </si>
+  <si>
+    <t>s'habiller</t>
+  </si>
+  <si>
+    <t>להתלבש</t>
+  </si>
+  <si>
+    <t>להתכתב</t>
+  </si>
+  <si>
+    <t>lehat’haïl</t>
+  </si>
+  <si>
+    <t>מתרגש</t>
+  </si>
+  <si>
+    <t>מתרגשת</t>
+  </si>
+  <si>
+    <t>מתרגשים</t>
+  </si>
+  <si>
+    <t>מתרגשות</t>
+  </si>
+  <si>
+    <t>leitragesh</t>
+  </si>
+  <si>
+    <t>מתרחץ</t>
+  </si>
+  <si>
+    <t>מתרחצת</t>
+  </si>
+  <si>
+    <t>מתרחצים</t>
+  </si>
+  <si>
+    <t>מתרחצות</t>
+  </si>
+  <si>
+    <t>leitrakhets</t>
+  </si>
+  <si>
+    <t>מתחתן</t>
+  </si>
+  <si>
+    <t>מתחתנת</t>
+  </si>
+  <si>
+    <t>מתחתנים</t>
+  </si>
+  <si>
+    <t>מתחתנות</t>
+  </si>
+  <si>
+    <t>lehitkhaten</t>
+  </si>
+  <si>
+    <t>מתלבש</t>
+  </si>
+  <si>
+    <t>מתלבשת</t>
+  </si>
+  <si>
+    <t>מתלבשים</t>
+  </si>
+  <si>
+    <t>מתלבשות</t>
+  </si>
+  <si>
+    <t>lehitlabesh</t>
+  </si>
+  <si>
+    <t>correspondre (écrire)</t>
+  </si>
+  <si>
+    <t>מתכתב</t>
+  </si>
+  <si>
+    <t>מתכתבת</t>
+  </si>
+  <si>
+    <t>מתכתבים</t>
+  </si>
+  <si>
+    <t>מתכתבות</t>
+  </si>
+  <si>
+    <t>lehitkatev</t>
+  </si>
+  <si>
+    <t>appel</t>
+  </si>
+  <si>
+    <t>météo</t>
+  </si>
+  <si>
+    <t>air</t>
+  </si>
+  <si>
+    <t>degré</t>
+  </si>
+  <si>
+    <t>ventilateur</t>
+  </si>
+  <si>
+    <t>pressing</t>
+  </si>
+  <si>
+    <t>facture</t>
+  </si>
+  <si>
+    <t>enveloppe</t>
+  </si>
+  <si>
+    <t>timbre</t>
+  </si>
+  <si>
+    <t>colis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vidéo </t>
+  </si>
+  <si>
+    <t>שיחה</t>
+  </si>
+  <si>
+    <t>sikha</t>
+  </si>
+  <si>
+    <t>שיחות</t>
+  </si>
+  <si>
+    <t>sikhot</t>
+  </si>
+  <si>
+    <t>appel téléphonique</t>
+  </si>
+  <si>
+    <t>שיחת טלפון</t>
+  </si>
+  <si>
+    <t>sikhat telefon</t>
+  </si>
+  <si>
+    <t>שיחות טלפון</t>
+  </si>
+  <si>
+    <t>sikhot telefon</t>
+  </si>
+  <si>
+    <t>מזג אוויר</t>
+  </si>
+  <si>
+    <t>mezeg avir</t>
+  </si>
+  <si>
+    <t>אוויר</t>
+  </si>
+  <si>
+    <t>avir</t>
+  </si>
+  <si>
+    <t>מעלה</t>
+  </si>
+  <si>
+    <t>ma'ala</t>
+  </si>
+  <si>
+    <t>מעלות</t>
+  </si>
+  <si>
+    <t>ma'alot</t>
+  </si>
+  <si>
+    <t>מאוורר</t>
+  </si>
+  <si>
+    <t>me’orer</t>
+  </si>
+  <si>
+    <t>מאווררים</t>
+  </si>
+  <si>
+    <t>me’or’rim</t>
+  </si>
+  <si>
+    <t>machine à laver</t>
+  </si>
+  <si>
+    <t>מכונת כביסה</t>
+  </si>
+  <si>
+    <t>mekhonat kvisa</t>
+  </si>
+  <si>
+    <t>מכונות כביסה</t>
+  </si>
+  <si>
+    <t>mekhonot kvisa</t>
+  </si>
+  <si>
+    <t>ניקוי יבש</t>
+  </si>
+  <si>
+    <t>nikouy yavesh</t>
+  </si>
+  <si>
+    <t>חשבונות</t>
+  </si>
+  <si>
+    <t>מעטפה</t>
+  </si>
+  <si>
+    <t>ma’atafa</t>
+  </si>
+  <si>
+    <t>מעטפות</t>
+  </si>
+  <si>
+    <t>ma’atafot</t>
+  </si>
+  <si>
+    <t>בול</t>
+  </si>
+  <si>
+    <t>boul</t>
+  </si>
+  <si>
+    <t>בולים</t>
+  </si>
+  <si>
+    <t>boulim</t>
+  </si>
+  <si>
+    <t>חבילה</t>
+  </si>
+  <si>
+    <t>חבילות</t>
+  </si>
+  <si>
+    <t>khavila</t>
+  </si>
+  <si>
+    <t>khavilot</t>
+  </si>
+  <si>
+    <t>kheshbon</t>
+  </si>
+  <si>
+    <t>kheshbonot</t>
   </si>
 </sst>
 </file>
@@ -9248,7 +9503,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -9610,42 +9865,36 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9716,10 +9965,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10061,10 +10306,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABE0CD65-8440-4615-80A1-7445699DAF7F}">
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="18.140625" style="91" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" style="91" customWidth="1"/>
     <col min="2" max="2" width="11.28515625" style="26" customWidth="1"/>
     <col min="3" max="3" width="11.140625" style="95" customWidth="1"/>
     <col min="4" max="4" width="12.28515625" style="95" customWidth="1"/>
@@ -10098,25 +10343,25 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="90" t="s">
+        <v>1808</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1807</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>1809</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>1808</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="94" t="s">
         <v>1810</v>
       </c>
-      <c r="D2" s="94" t="s">
+      <c r="E2" s="97" t="s">
         <v>1811</v>
       </c>
-      <c r="E2" s="97" t="s">
+      <c r="F2" s="98" t="s">
         <v>1812</v>
       </c>
-      <c r="F2" s="98" t="s">
+      <c r="G2" s="1" t="s">
         <v>1813</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>1814</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -10259,30 +10504,30 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="13" t="s">
+        <v>2425</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>2426</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>2427</v>
+      </c>
+      <c r="E9" s="99" t="s">
         <v>2428</v>
       </c>
-      <c r="B9" s="21" t="s">
-        <v>2426</v>
-      </c>
-      <c r="C9" s="11" t="s">
+      <c r="F9" s="99" t="s">
         <v>2429</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="G9" s="9" t="s">
         <v>2430</v>
-      </c>
-      <c r="E9" s="99" t="s">
-        <v>2431</v>
-      </c>
-      <c r="F9" s="99" t="s">
-        <v>2432</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>2433</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="90" t="s">
-        <v>2310</v>
+        <v>2307</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>344</v>
@@ -10300,7 +10545,7 @@
         <v>348</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -10374,48 +10619,48 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="13" t="s">
-        <v>2419</v>
+        <v>2416</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>2424</v>
+        <v>2421</v>
       </c>
       <c r="C14" s="11" t="s">
+        <v>2436</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>2437</v>
+      </c>
+      <c r="E14" s="99" t="s">
+        <v>2438</v>
+      </c>
+      <c r="F14" s="99" t="s">
         <v>2439</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="G14" s="9" t="s">
         <v>2440</v>
-      </c>
-      <c r="E14" s="99" t="s">
-        <v>2441</v>
-      </c>
-      <c r="F14" s="99" t="s">
-        <v>2442</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>2443</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="13" t="s">
-        <v>2421</v>
+        <v>2418</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>2422</v>
+        <v>2419</v>
       </c>
       <c r="C15" s="11" t="s">
+        <v>2446</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>2447</v>
+      </c>
+      <c r="E15" s="99" t="s">
+        <v>2448</v>
+      </c>
+      <c r="F15" s="99" t="s">
         <v>2449</v>
       </c>
-      <c r="D15" s="11" t="s">
-        <v>2450</v>
-      </c>
-      <c r="E15" s="99" t="s">
-        <v>2451</v>
-      </c>
-      <c r="F15" s="99" t="s">
-        <v>2452</v>
-      </c>
       <c r="G15" s="9" t="s">
-        <v>2453</v>
+        <v>2937</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -10516,331 +10761,331 @@
         <v>374</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="90" t="s">
-        <v>367</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="E20" s="97" t="s">
-        <v>390</v>
-      </c>
-      <c r="F20" s="97" t="s">
-        <v>391</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>368</v>
+    <row r="20" spans="1:7" ht="31.5">
+      <c r="A20" s="80" t="s">
+        <v>2958</v>
+      </c>
+      <c r="B20" s="80" t="s">
+        <v>2936</v>
+      </c>
+      <c r="C20" s="80" t="s">
+        <v>2959</v>
+      </c>
+      <c r="D20" s="80" t="s">
+        <v>2960</v>
+      </c>
+      <c r="E20" s="80" t="s">
+        <v>2961</v>
+      </c>
+      <c r="F20" s="80" t="s">
+        <v>2962</v>
+      </c>
+      <c r="G20" s="80" t="s">
+        <v>2963</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="90" t="s">
-        <v>1274</v>
-      </c>
-      <c r="B21" s="23" t="s">
-        <v>1275</v>
-      </c>
-      <c r="C21" s="94" t="s">
-        <v>1277</v>
-      </c>
-      <c r="D21" s="94" t="s">
-        <v>1278</v>
-      </c>
-      <c r="E21" s="98" t="s">
-        <v>1279</v>
-      </c>
-      <c r="F21" s="98" t="s">
-        <v>1280</v>
+        <v>367</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="E21" s="97" t="s">
+        <v>390</v>
+      </c>
+      <c r="F21" s="97" t="s">
+        <v>391</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>1276</v>
+        <v>368</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="90" t="s">
-        <v>1330</v>
+        <v>1274</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>2410</v>
+        <v>1275</v>
       </c>
       <c r="C22" s="94" t="s">
-        <v>2412</v>
+        <v>1277</v>
       </c>
       <c r="D22" s="94" t="s">
-        <v>2413</v>
+        <v>1278</v>
       </c>
       <c r="E22" s="98" t="s">
-        <v>2414</v>
+        <v>1279</v>
       </c>
       <c r="F22" s="98" t="s">
-        <v>2415</v>
+        <v>1280</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>2411</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="90" t="s">
-        <v>1281</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>1284</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>1285</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>1286</v>
-      </c>
-      <c r="E23" s="97" t="s">
-        <v>1287</v>
-      </c>
-      <c r="F23" s="97" t="s">
-        <v>1288</v>
+        <v>1330</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>2407</v>
+      </c>
+      <c r="C23" s="94" t="s">
+        <v>2409</v>
+      </c>
+      <c r="D23" s="94" t="s">
+        <v>2410</v>
+      </c>
+      <c r="E23" s="98" t="s">
+        <v>2411</v>
+      </c>
+      <c r="F23" s="98" t="s">
+        <v>2412</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>1289</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="90" t="s">
-        <v>38</v>
+        <v>1281</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>39</v>
+        <v>1284</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>40</v>
+        <v>1285</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>288</v>
+        <v>1286</v>
       </c>
       <c r="E24" s="97" t="s">
-        <v>41</v>
+        <v>1287</v>
       </c>
       <c r="F24" s="97" t="s">
-        <v>289</v>
+        <v>1288</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>42</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="90" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E25" s="97" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F25" s="97" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="90" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E26" s="97" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F26" s="97" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="90" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E27" s="97" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F27" s="97" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="90" t="s">
-        <v>1328</v>
+        <v>53</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>1332</v>
+        <v>54</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>1333</v>
+        <v>55</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>1334</v>
+        <v>294</v>
       </c>
       <c r="E28" s="97" t="s">
-        <v>1335</v>
+        <v>56</v>
       </c>
       <c r="F28" s="97" t="s">
-        <v>1336</v>
+        <v>295</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>1337</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="90" t="s">
-        <v>58</v>
+        <v>1328</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>59</v>
+        <v>1332</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>60</v>
+        <v>1333</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>296</v>
+        <v>1334</v>
       </c>
       <c r="E29" s="97" t="s">
-        <v>61</v>
+        <v>1335</v>
       </c>
       <c r="F29" s="97" t="s">
-        <v>297</v>
+        <v>1336</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>62</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="90" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E30" s="97" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F30" s="97" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="90" t="s">
-        <v>216</v>
+        <v>63</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>338</v>
+        <v>64</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>337</v>
+        <v>65</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>339</v>
+        <v>298</v>
       </c>
       <c r="E31" s="97" t="s">
-        <v>340</v>
+        <v>66</v>
       </c>
       <c r="F31" s="97" t="s">
-        <v>341</v>
+        <v>299</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>218</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="90" t="s">
+        <v>216</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="E32" s="97" t="s">
+        <v>340</v>
+      </c>
+      <c r="F32" s="97" t="s">
+        <v>341</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="90" t="s">
         <v>68</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B33" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C33" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D33" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="E32" s="97" t="s">
+      <c r="E33" s="97" t="s">
         <v>71</v>
       </c>
-      <c r="F32" s="97" t="s">
+      <c r="F33" s="97" t="s">
         <v>300</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G33" s="1" t="s">
         <v>165</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="B33" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="E33" s="99" t="s">
-        <v>71</v>
-      </c>
-      <c r="F33" s="99" t="s">
-        <v>300</v>
-      </c>
-      <c r="G33" s="59" t="s">
-        <v>2461</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="37.5">
       <c r="A34" s="13" t="s">
-        <v>2566</v>
+        <v>2561</v>
       </c>
       <c r="B34" s="21" t="s">
         <v>98</v>
@@ -10849,7 +11094,7 @@
         <v>99</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>2567</v>
+        <v>2562</v>
       </c>
       <c r="E34" s="99" t="s">
         <v>100</v>
@@ -10863,10 +11108,10 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="90" t="s">
-        <v>2323</v>
+        <v>2320</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>2324</v>
+        <v>2321</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>217</v>
@@ -10881,30 +11126,30 @@
         <v>217</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>2325</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="13" t="s">
-        <v>2418</v>
+        <v>2415</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>2425</v>
+        <v>2422</v>
       </c>
       <c r="C36" s="11" t="s">
+        <v>2431</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>2432</v>
+      </c>
+      <c r="E36" s="99" t="s">
+        <v>2433</v>
+      </c>
+      <c r="F36" s="99" t="s">
         <v>2434</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="G36" s="9" t="s">
         <v>2435</v>
-      </c>
-      <c r="E36" s="99" t="s">
-        <v>2436</v>
-      </c>
-      <c r="F36" s="99" t="s">
-        <v>2437</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>2438</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -10955,25 +11200,25 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="90" t="s">
-        <v>2409</v>
+        <v>2406</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>2325</v>
+      </c>
+      <c r="D39" s="6" t="s">
         <v>2326</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="E39" s="97" t="s">
+        <v>2327</v>
+      </c>
+      <c r="F39" s="97" t="s">
         <v>2328</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>2329</v>
-      </c>
-      <c r="E39" s="97" t="s">
-        <v>2330</v>
-      </c>
-      <c r="F39" s="97" t="s">
-        <v>2331</v>
-      </c>
       <c r="G39" s="1" t="s">
-        <v>2327</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -11001,25 +11246,25 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="90" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="C41" s="94" t="s">
         <v>941</v>
       </c>
       <c r="D41" s="94" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="E41" s="98" t="s">
         <v>1037</v>
       </c>
       <c r="F41" s="98" t="s">
+        <v>1805</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>1806</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>1807</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -11139,25 +11384,25 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="90" t="s">
-        <v>2333</v>
+        <v>2330</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>2332</v>
+        <v>2329</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>189</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>2335</v>
+        <v>2332</v>
       </c>
       <c r="E47" s="97" t="s">
-        <v>2336</v>
+        <v>2333</v>
       </c>
       <c r="F47" s="97" t="s">
-        <v>2337</v>
+        <v>2334</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>2334</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -11208,25 +11453,25 @@
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="90" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>1815</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="C50" s="6" t="s">
         <v>1816</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="D50" s="6" t="s">
         <v>1817</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="E50" s="97" t="s">
         <v>1818</v>
       </c>
-      <c r="E50" s="97" t="s">
+      <c r="F50" s="97" t="s">
         <v>1819</v>
       </c>
-      <c r="F50" s="97" t="s">
+      <c r="G50" s="1" t="s">
         <v>1820</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>1821</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -11252,7 +11497,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="20.25" customHeight="1">
+    <row r="52" spans="1:10">
       <c r="A52" s="90" t="s">
         <v>107</v>
       </c>
@@ -11320,7 +11565,6 @@
       <c r="G54" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="I54" s="29"/>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="90" t="s">
@@ -11344,9 +11588,8 @@
       <c r="G55" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="I55" s="29"/>
-    </row>
-    <row r="56" spans="1:10">
+    </row>
+    <row r="56" spans="1:10" ht="20.25" customHeight="1">
       <c r="A56" s="90" t="s">
         <v>1267</v>
       </c>
@@ -11368,7 +11611,6 @@
       <c r="G56" s="1" t="s">
         <v>1272</v>
       </c>
-      <c r="I56" s="29"/>
     </row>
     <row r="57" spans="1:10" ht="37.5">
       <c r="A57" s="13" t="s">
@@ -11392,7 +11634,6 @@
       <c r="G57" s="1" t="s">
         <v>1359</v>
       </c>
-      <c r="J57" s="29"/>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="90" t="s">
@@ -11416,9 +11657,7 @@
       <c r="G58" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="J58" s="29" t="s">
-        <v>217</v>
-      </c>
+      <c r="I58" s="29"/>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="90" t="s">
@@ -11442,33 +11681,31 @@
       <c r="G59" s="1" t="s">
         <v>1374</v>
       </c>
-      <c r="J59" s="29"/>
+      <c r="I59" s="29"/>
     </row>
     <row r="60" spans="1:10" ht="37.5">
       <c r="A60" s="13" t="s">
+        <v>2450</v>
+      </c>
+      <c r="B60" s="21" t="s">
+        <v>2424</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>2451</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>2452</v>
+      </c>
+      <c r="E60" s="99" t="s">
+        <v>2453</v>
+      </c>
+      <c r="F60" s="99" t="s">
         <v>2454</v>
       </c>
-      <c r="B60" s="21" t="s">
-        <v>2427</v>
-      </c>
-      <c r="C60" s="11" t="s">
+      <c r="G60" s="9" t="s">
         <v>2455</v>
       </c>
-      <c r="D60" s="11" t="s">
-        <v>2456</v>
-      </c>
-      <c r="E60" s="99" t="s">
-        <v>2457</v>
-      </c>
-      <c r="F60" s="99" t="s">
-        <v>2458</v>
-      </c>
-      <c r="G60" s="9" t="s">
-        <v>2459</v>
-      </c>
-      <c r="J60" s="29" t="s">
-        <v>217</v>
-      </c>
+      <c r="I60" s="29"/>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="90" t="s">
@@ -11492,9 +11729,7 @@
       <c r="G61" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="J61" s="29" t="s">
-        <v>217</v>
-      </c>
+      <c r="J61" s="29"/>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="90" t="s">
@@ -11544,9 +11779,7 @@
       <c r="G63" s="1" t="s">
         <v>1369</v>
       </c>
-      <c r="J63" s="29" t="s">
-        <v>217</v>
-      </c>
+      <c r="J63" s="29"/>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="90" t="s">
@@ -11570,309 +11803,413 @@
       <c r="G64" s="1" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="65" spans="1:7">
-      <c r="A65" s="90" t="s">
+      <c r="J64" s="29" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="15.75">
+      <c r="A65" s="80" t="s">
+        <v>2930</v>
+      </c>
+      <c r="B65" s="80" t="s">
+        <v>2931</v>
+      </c>
+      <c r="C65" s="80" t="s">
+        <v>2943</v>
+      </c>
+      <c r="D65" s="80" t="s">
+        <v>2944</v>
+      </c>
+      <c r="E65" s="80" t="s">
+        <v>2945</v>
+      </c>
+      <c r="F65" s="80" t="s">
+        <v>2946</v>
+      </c>
+      <c r="G65" s="80" t="s">
+        <v>2947</v>
+      </c>
+      <c r="J65" s="29" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" s="90" t="s">
         <v>131</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B66" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C66" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="D65" s="6" t="s">
+      <c r="D66" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="E65" s="97" t="s">
+      <c r="E66" s="97" t="s">
         <v>134</v>
       </c>
-      <c r="F65" s="97" t="s">
+      <c r="F66" s="97" t="s">
         <v>327</v>
       </c>
-      <c r="G65" s="1" t="s">
+      <c r="G66" s="1" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="66" spans="1:7">
-      <c r="A66" s="90" t="s">
+      <c r="J66" s="29" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="15.75">
+      <c r="A67" s="80" t="s">
+        <v>2933</v>
+      </c>
+      <c r="B67" s="80" t="s">
+        <v>2932</v>
+      </c>
+      <c r="C67" s="80" t="s">
+        <v>2948</v>
+      </c>
+      <c r="D67" s="80" t="s">
+        <v>2949</v>
+      </c>
+      <c r="E67" s="80" t="s">
+        <v>2950</v>
+      </c>
+      <c r="F67" s="80" t="s">
+        <v>2951</v>
+      </c>
+      <c r="G67" s="80" t="s">
+        <v>2952</v>
+      </c>
+      <c r="J67" s="29" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" s="90" t="s">
         <v>135</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B68" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C66" s="6" t="s">
+      <c r="C68" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D66" s="6" t="s">
+      <c r="D68" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="E66" s="97" t="s">
+      <c r="E68" s="97" t="s">
         <v>138</v>
       </c>
-      <c r="F66" s="97" t="s">
+      <c r="F68" s="97" t="s">
         <v>329</v>
       </c>
-      <c r="G66" s="1" t="s">
+      <c r="G68" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="37.5">
-      <c r="A67" s="13" t="s">
+    <row r="69" spans="1:10" ht="37.5">
+      <c r="A69" s="13" t="s">
+        <v>2417</v>
+      </c>
+      <c r="B69" s="21" t="s">
         <v>2420</v>
       </c>
-      <c r="B67" s="21" t="s">
-        <v>2423</v>
-      </c>
-      <c r="C67" s="11" t="s">
+      <c r="C69" s="11" t="s">
+        <v>2441</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>2442</v>
+      </c>
+      <c r="E69" s="99" t="s">
+        <v>2443</v>
+      </c>
+      <c r="F69" s="99" t="s">
         <v>2444</v>
       </c>
-      <c r="D67" s="11" t="s">
+      <c r="G69" s="9" t="s">
         <v>2445</v>
       </c>
-      <c r="E67" s="99" t="s">
-        <v>2446</v>
-      </c>
-      <c r="F67" s="99" t="s">
-        <v>2447</v>
-      </c>
-      <c r="G67" s="9" t="s">
-        <v>2448</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
-      <c r="A68" s="90" t="s">
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" s="90" t="s">
+        <v>2335</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>2336</v>
+      </c>
+      <c r="C70" s="6" t="s">
         <v>2338</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="D70" s="6" t="s">
         <v>2339</v>
       </c>
-      <c r="C68" s="6" t="s">
+      <c r="E70" s="97" t="s">
+        <v>2340</v>
+      </c>
+      <c r="F70" s="97" t="s">
         <v>2341</v>
       </c>
-      <c r="D68" s="6" t="s">
-        <v>2342</v>
-      </c>
-      <c r="E68" s="97" t="s">
-        <v>2343</v>
-      </c>
-      <c r="F68" s="97" t="s">
-        <v>2344</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>2340</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
-      <c r="A69" s="90" t="s">
+      <c r="G70" s="1" t="s">
+        <v>2337</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="15.75">
+      <c r="A71" s="80" t="s">
+        <v>2928</v>
+      </c>
+      <c r="B71" s="80" t="s">
+        <v>2929</v>
+      </c>
+      <c r="C71" s="80" t="s">
+        <v>2938</v>
+      </c>
+      <c r="D71" s="80" t="s">
+        <v>2939</v>
+      </c>
+      <c r="E71" s="80" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F71" s="80" t="s">
+        <v>2941</v>
+      </c>
+      <c r="G71" s="80" t="s">
+        <v>2942</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="15.75">
+      <c r="A72" s="80" t="s">
+        <v>2934</v>
+      </c>
+      <c r="B72" s="80" t="s">
+        <v>2935</v>
+      </c>
+      <c r="C72" s="80" t="s">
+        <v>2953</v>
+      </c>
+      <c r="D72" s="80" t="s">
+        <v>2954</v>
+      </c>
+      <c r="E72" s="80" t="s">
+        <v>2955</v>
+      </c>
+      <c r="F72" s="80" t="s">
+        <v>2956</v>
+      </c>
+      <c r="G72" s="80" t="s">
+        <v>2957</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" s="90" t="s">
+        <v>2299</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>2300</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>2303</v>
+      </c>
+      <c r="D73" s="6" t="s">
         <v>2302</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>2303</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>2306</v>
-      </c>
-      <c r="D69" s="6" t="s">
+      <c r="E73" s="97" t="s">
+        <v>2304</v>
+      </c>
+      <c r="F73" s="97" t="s">
         <v>2305</v>
       </c>
-      <c r="E69" s="97" t="s">
-        <v>2307</v>
-      </c>
-      <c r="F69" s="97" t="s">
-        <v>2308</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>2304</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70" s="90" t="s">
+      <c r="G73" s="1" t="s">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" s="90" t="s">
         <v>140</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B74" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C70" s="6" t="s">
+      <c r="C74" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D70" s="6" t="s">
+      <c r="D74" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="E70" s="97" t="s">
+      <c r="E74" s="97" t="s">
         <v>143</v>
       </c>
-      <c r="F70" s="97" t="s">
+      <c r="F74" s="97" t="s">
         <v>331</v>
       </c>
-      <c r="G70" s="1" t="s">
+      <c r="G74" s="1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
-      <c r="A71" s="90" t="s">
+    <row r="75" spans="1:10">
+      <c r="A75" s="90" t="s">
+        <v>2292</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>2293</v>
+      </c>
+      <c r="C75" s="6" t="s">
         <v>2295</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="D75" s="6" t="s">
         <v>2296</v>
       </c>
-      <c r="C71" s="6" t="s">
+      <c r="E75" s="97" t="s">
+        <v>2297</v>
+      </c>
+      <c r="F75" s="97" t="s">
         <v>2298</v>
       </c>
-      <c r="D71" s="6" t="s">
-        <v>2299</v>
-      </c>
-      <c r="E71" s="97" t="s">
-        <v>2300</v>
-      </c>
-      <c r="F71" s="97" t="s">
-        <v>2301</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>2297</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7">
-      <c r="A72" s="90" t="s">
+      <c r="G75" s="1" t="s">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" s="90" t="s">
         <v>145</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B76" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C72" s="6" t="s">
+      <c r="C76" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="D72" s="6" t="s">
+      <c r="D76" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="E72" s="97" t="s">
+      <c r="E76" s="97" t="s">
         <v>148</v>
       </c>
-      <c r="F72" s="97" t="s">
+      <c r="F76" s="97" t="s">
         <v>333</v>
       </c>
-      <c r="G72" s="1" t="s">
+      <c r="G76" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
-      <c r="A73" s="90" t="s">
+    <row r="77" spans="1:10">
+      <c r="A77" s="90" t="s">
         <v>1329</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B77" s="3" t="s">
         <v>1348</v>
       </c>
-      <c r="C73" s="6" t="s">
+      <c r="C77" s="6" t="s">
         <v>1349</v>
       </c>
-      <c r="D73" s="6" t="s">
+      <c r="D77" s="6" t="s">
         <v>1349</v>
       </c>
-      <c r="E73" s="97" t="s">
+      <c r="E77" s="97" t="s">
         <v>1350</v>
       </c>
-      <c r="F73" s="97" t="s">
+      <c r="F77" s="97" t="s">
         <v>1351</v>
       </c>
-      <c r="G73" s="1" t="s">
+      <c r="G77" s="1" t="s">
         <v>1352</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
-      <c r="A74" s="88" t="s">
+    <row r="78" spans="1:10">
+      <c r="A78" s="88" t="s">
+        <v>2457</v>
+      </c>
+      <c r="B78" s="92" t="s">
+        <v>2458</v>
+      </c>
+      <c r="C78" s="11" t="s">
+        <v>2459</v>
+      </c>
+      <c r="D78" s="11" t="s">
+        <v>2460</v>
+      </c>
+      <c r="E78" s="99" t="s">
+        <v>2461</v>
+      </c>
+      <c r="F78" s="99" t="s">
         <v>2462</v>
       </c>
-      <c r="B74" s="92" t="s">
+      <c r="G78" s="59" t="s">
         <v>2463</v>
       </c>
-      <c r="C74" s="11" t="s">
-        <v>2464</v>
-      </c>
-      <c r="D74" s="11" t="s">
-        <v>2465</v>
-      </c>
-      <c r="E74" s="99" t="s">
-        <v>2466</v>
-      </c>
-      <c r="F74" s="99" t="s">
-        <v>2467</v>
-      </c>
-      <c r="G74" s="59" t="s">
-        <v>2468</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7">
-      <c r="A75" s="90" t="s">
+    </row>
+    <row r="79" spans="1:10">
+      <c r="A79" s="90" t="s">
         <v>349</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B79" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="C75" s="6" t="s">
+      <c r="C79" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="D75" s="6" t="s">
+      <c r="D79" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="E75" s="97" t="s">
+      <c r="E79" s="97" t="s">
         <v>354</v>
       </c>
-      <c r="F75" s="97" t="s">
+      <c r="F79" s="97" t="s">
         <v>355</v>
       </c>
-      <c r="G75" s="1" t="s">
+      <c r="G79" s="1" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
-      <c r="A76" s="90" t="s">
+    <row r="80" spans="1:10">
+      <c r="A80" s="90" t="s">
         <v>155</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B80" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C76" s="6" t="s">
+      <c r="C80" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="D76" s="6" t="s">
+      <c r="D80" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="E76" s="97" t="s">
+      <c r="E80" s="97" t="s">
         <v>158</v>
       </c>
-      <c r="F76" s="97" t="s">
-        <v>2322</v>
-      </c>
-      <c r="G76" s="1" t="s">
+      <c r="F80" s="97" t="s">
+        <v>2319</v>
+      </c>
+      <c r="G80" s="1" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
-      <c r="A77" s="90" t="s">
+    <row r="81" spans="1:7">
+      <c r="A81" s="90" t="s">
         <v>150</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B81" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C77" s="6" t="s">
+      <c r="C81" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="D77" s="6" t="s">
+      <c r="D81" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="E77" s="97" t="s">
+      <c r="E81" s="97" t="s">
         <v>153</v>
       </c>
-      <c r="F77" s="97" t="s">
+      <c r="F81" s="97" t="s">
         <v>335</v>
       </c>
-      <c r="G77" s="1" t="s">
+      <c r="G81" s="1" t="s">
         <v>154</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G77">
-    <sortCondition ref="A2:A77"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G81">
+    <sortCondition ref="A2:A81"/>
   </sortState>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -11885,9 +12222,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.5703125" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" style="149"/>
     <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="154"/>
     <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -11895,13 +12230,13 @@
       <c r="A1" s="46" t="s">
         <v>1506</v>
       </c>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="144" t="s">
         <v>831</v>
       </c>
       <c r="C1" s="38" t="s">
         <v>1519</v>
       </c>
-      <c r="D1" s="150" t="s">
+      <c r="D1" s="38" t="s">
         <v>1694</v>
       </c>
       <c r="E1" s="38" t="s">
@@ -11910,53 +12245,53 @@
     </row>
     <row r="2" spans="1:5" ht="18.75">
       <c r="A2" s="6" t="s">
+        <v>1945</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>1946</v>
       </c>
-      <c r="B2" s="147" t="s">
+      <c r="C2" s="18" t="s">
         <v>1947</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="D2" s="145" t="s">
         <v>1948</v>
       </c>
-      <c r="D2" s="151" t="s">
+      <c r="E2" s="18" t="s">
         <v>1949</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>1950</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18.75">
       <c r="A3" s="11" t="s">
+        <v>2355</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>2356</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>2357</v>
+      </c>
+      <c r="D3" s="146" t="s">
         <v>2358</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="E3" s="9" t="s">
         <v>2359</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>2360</v>
-      </c>
-      <c r="D3" s="152" t="s">
-        <v>2361</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>2362</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18.75">
       <c r="A4" s="11" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="B4" s="9" t="s">
+        <v>1941</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>1943</v>
+      </c>
+      <c r="D4" s="146" t="s">
         <v>1942</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="E4" s="9" t="s">
         <v>1944</v>
-      </c>
-      <c r="D4" s="152" t="s">
-        <v>1943</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>1945</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18.75">
@@ -11969,7 +12304,7 @@
       <c r="C5" s="9" t="s">
         <v>830</v>
       </c>
-      <c r="D5" s="152" t="s">
+      <c r="D5" s="146" t="s">
         <v>1028</v>
       </c>
       <c r="E5" s="9" t="s">
@@ -11986,7 +12321,7 @@
       <c r="C6" s="9" t="s">
         <v>1531</v>
       </c>
-      <c r="D6" s="152" t="s">
+      <c r="D6" s="146" t="s">
         <v>1532</v>
       </c>
       <c r="E6" s="9" t="s">
@@ -12003,7 +12338,7 @@
       <c r="C7" s="9" t="s">
         <v>1519</v>
       </c>
-      <c r="D7" s="152" t="s">
+      <c r="D7" s="146" t="s">
         <v>1030</v>
       </c>
       <c r="E7" s="9" t="s">
@@ -12020,7 +12355,7 @@
       <c r="C8" s="9" t="s">
         <v>1531</v>
       </c>
-      <c r="D8" s="152" t="s">
+      <c r="D8" s="146" t="s">
         <v>1532</v>
       </c>
       <c r="E8" s="9" t="s">
@@ -12029,15 +12364,15 @@
     </row>
     <row r="9" spans="1:5" ht="18.75">
       <c r="A9" s="11" t="s">
-        <v>2630</v>
-      </c>
-      <c r="B9" s="148" t="s">
+        <v>2625</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>1570</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>1569</v>
       </c>
-      <c r="D9" s="153" t="s">
+      <c r="D9" s="147" t="s">
         <v>1571</v>
       </c>
       <c r="E9" s="9" t="s">
@@ -12046,7 +12381,7 @@
     </row>
     <row r="10" spans="1:5" ht="37.5">
       <c r="A10" s="11" t="s">
-        <v>2629</v>
+        <v>2624</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>1534</v>
@@ -12054,7 +12389,7 @@
       <c r="C10" s="9" t="s">
         <v>1535</v>
       </c>
-      <c r="D10" s="152" t="s">
+      <c r="D10" s="146" t="s">
         <v>1536</v>
       </c>
       <c r="E10" s="9" t="s">
@@ -12071,7 +12406,7 @@
       <c r="C11" s="9" t="s">
         <v>1539</v>
       </c>
-      <c r="D11" s="152" t="s">
+      <c r="D11" s="146" t="s">
         <v>1540</v>
       </c>
       <c r="E11" s="9" t="s">
@@ -12088,7 +12423,7 @@
       <c r="C12" s="9" t="s">
         <v>830</v>
       </c>
-      <c r="D12" s="152" t="s">
+      <c r="D12" s="146" t="s">
         <v>1028</v>
       </c>
       <c r="E12" s="9" t="s">
@@ -12097,19 +12432,19 @@
     </row>
     <row r="13" spans="1:5" ht="18.75">
       <c r="A13" s="9" t="s">
-        <v>2633</v>
+        <v>2628</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>2631</v>
-      </c>
-      <c r="C13" s="145" t="s">
+        <v>2626</v>
+      </c>
+      <c r="C13" s="143" t="s">
+        <v>2627</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>2632</v>
       </c>
-      <c r="D13" s="148" t="s">
-        <v>2637</v>
-      </c>
       <c r="E13" s="1" t="s">
-        <v>2639</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="37.5">
@@ -12122,7 +12457,7 @@
       <c r="C14" s="9" t="s">
         <v>1548</v>
       </c>
-      <c r="D14" s="152" t="s">
+      <c r="D14" s="146" t="s">
         <v>1549</v>
       </c>
       <c r="E14" s="9" t="s">
@@ -12139,7 +12474,7 @@
       <c r="C15" s="9" t="s">
         <v>1553</v>
       </c>
-      <c r="D15" s="152" t="s">
+      <c r="D15" s="146" t="s">
         <v>1554</v>
       </c>
       <c r="E15" s="9" t="s">
@@ -12156,7 +12491,7 @@
       <c r="C16" s="9" t="s">
         <v>1527</v>
       </c>
-      <c r="D16" s="152" t="s">
+      <c r="D16" s="146" t="s">
         <v>1528</v>
       </c>
       <c r="E16" s="9" t="s">
@@ -12165,19 +12500,19 @@
     </row>
     <row r="17" spans="1:5" ht="37.5">
       <c r="A17" s="9" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>2634</v>
-      </c>
-      <c r="C17" s="145" t="s">
+        <v>2629</v>
+      </c>
+      <c r="C17" s="143" t="s">
+        <v>2630</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>2633</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>2635</v>
-      </c>
-      <c r="D17" s="148" t="s">
-        <v>2638</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>2640</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18.75">
@@ -12185,12 +12520,12 @@
         <v>1567</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>2417</v>
+        <v>2414</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>1568</v>
       </c>
-      <c r="D18" s="153" t="s">
+      <c r="D18" s="147" t="s">
         <v>1565</v>
       </c>
       <c r="E18" s="9" t="s">
@@ -12207,7 +12542,7 @@
       <c r="C19" s="9" t="s">
         <v>1557</v>
       </c>
-      <c r="D19" s="152" t="s">
+      <c r="D19" s="146" t="s">
         <v>1558</v>
       </c>
       <c r="E19" s="9" t="s">
@@ -12224,7 +12559,7 @@
       <c r="C20" s="9" t="s">
         <v>1523</v>
       </c>
-      <c r="D20" s="152" t="s">
+      <c r="D20" s="146" t="s">
         <v>1524</v>
       </c>
       <c r="E20" s="9" t="s">
@@ -12241,7 +12576,7 @@
       <c r="C21" s="9" t="s">
         <v>1562</v>
       </c>
-      <c r="D21" s="152" t="s">
+      <c r="D21" s="146" t="s">
         <v>1563</v>
       </c>
       <c r="E21" s="9" t="s">
@@ -12258,7 +12593,7 @@
       <c r="C22" s="9" t="s">
         <v>1081</v>
       </c>
-      <c r="D22" s="152" t="s">
+      <c r="D22" s="146" t="s">
         <v>881</v>
       </c>
       <c r="E22" s="9" t="s">
@@ -12275,7 +12610,7 @@
       <c r="C23" s="9" t="s">
         <v>1543</v>
       </c>
-      <c r="D23" s="152" t="s">
+      <c r="D23" s="146" t="s">
         <v>1544</v>
       </c>
       <c r="E23" s="9" t="s">
@@ -12306,187 +12641,187 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.75">
       <c r="A1" s="9" t="s">
-        <v>2704</v>
+        <v>2699</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>2714</v>
+        <v>2709</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>2715</v>
+        <v>2710</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>2716</v>
+        <v>2711</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>2717</v>
-      </c>
-      <c r="F1" s="145" t="s">
-        <v>2718</v>
+        <v>2712</v>
+      </c>
+      <c r="F1" s="143" t="s">
+        <v>2713</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="18.75">
       <c r="A2" s="9" t="s">
-        <v>2381</v>
+        <v>2378</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>2382</v>
+        <v>2379</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>2382</v>
+        <v>2379</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>2383</v>
+        <v>2380</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>2705</v>
-      </c>
-      <c r="F2" s="145" t="s">
-        <v>2706</v>
+        <v>2700</v>
+      </c>
+      <c r="F2" s="143" t="s">
+        <v>2701</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="18.75">
       <c r="A3" s="9" t="s">
-        <v>2683</v>
+        <v>2678</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>2684</v>
+        <v>2679</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>2685</v>
+        <v>2680</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>2686</v>
+        <v>2681</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>2687</v>
-      </c>
-      <c r="F3" s="145" t="s">
-        <v>2701</v>
+        <v>2682</v>
+      </c>
+      <c r="F3" s="143" t="s">
+        <v>2696</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="18.75">
       <c r="A4" s="9" t="s">
-        <v>2678</v>
+        <v>2673</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>2679</v>
+        <v>2674</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>2680</v>
+        <v>2675</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>2681</v>
+        <v>2676</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>2682</v>
-      </c>
-      <c r="F4" s="145" t="s">
-        <v>2700</v>
+        <v>2677</v>
+      </c>
+      <c r="F4" s="143" t="s">
+        <v>2695</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="18.75">
       <c r="A5" s="9" t="s">
-        <v>2731</v>
+        <v>2726</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>2373</v>
+        <v>2370</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>2671</v>
+        <v>2666</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>2375</v>
+        <v>2372</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>2672</v>
-      </c>
-      <c r="F5" s="145" t="s">
-        <v>2374</v>
+        <v>2667</v>
+      </c>
+      <c r="F5" s="143" t="s">
+        <v>2371</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="22.5" customHeight="1">
       <c r="A6" s="9" t="s">
+        <v>2720</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>2721</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>2722</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>2723</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>2724</v>
+      </c>
+      <c r="F6" s="143" t="s">
         <v>2725</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>2726</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>2727</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>2728</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>2729</v>
-      </c>
-      <c r="F6" s="145" t="s">
-        <v>2730</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18.75">
       <c r="A7" s="9" t="s">
-        <v>2732</v>
+        <v>2727</v>
       </c>
       <c r="B7" s="9" t="s">
+        <v>2325</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>2326</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>2327</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>2328</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>2329</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>2330</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>2331</v>
-      </c>
-      <c r="F7" s="145" t="s">
-        <v>2736</v>
+      <c r="F7" s="143" t="s">
+        <v>2731</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="18.75">
       <c r="A8" s="9" t="s">
-        <v>2673</v>
+        <v>2668</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>2674</v>
+        <v>2669</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>2675</v>
+        <v>2670</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>2676</v>
+        <v>2671</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>2677</v>
-      </c>
-      <c r="F8" s="145" t="s">
-        <v>2699</v>
+        <v>2672</v>
+      </c>
+      <c r="F8" s="143" t="s">
+        <v>2694</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18.75">
       <c r="A9" s="9" t="s">
-        <v>2408</v>
+        <v>2405</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>2376</v>
+        <v>2373</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>2707</v>
+        <v>2702</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>2378</v>
+        <v>2375</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>2708</v>
-      </c>
-      <c r="F9" s="145" t="s">
-        <v>2377</v>
+        <v>2703</v>
+      </c>
+      <c r="F9" s="143" t="s">
+        <v>2374</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="18.75">
       <c r="A10" s="9" t="s">
-        <v>2734</v>
+        <v>2729</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>1371</v>
@@ -12500,53 +12835,53 @@
       <c r="E10" s="9" t="s">
         <v>1373</v>
       </c>
-      <c r="F10" s="145" t="s">
-        <v>2735</v>
+      <c r="F10" s="143" t="s">
+        <v>2730</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="37.5">
       <c r="A11" s="9" t="s">
+        <v>2714</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>2715</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>2716</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>2717</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>2718</v>
+      </c>
+      <c r="F11" s="143" t="s">
         <v>2719</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>2720</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>2721</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>2722</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>2723</v>
-      </c>
-      <c r="F11" s="145" t="s">
-        <v>2724</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="18.75">
       <c r="A12" s="9" t="s">
-        <v>2688</v>
+        <v>2683</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>2690</v>
+        <v>2685</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>2692</v>
-      </c>
-      <c r="F12" s="145" t="s">
-        <v>2702</v>
+        <v>2687</v>
+      </c>
+      <c r="F12" s="143" t="s">
+        <v>2697</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="18.75">
       <c r="A13" s="9" t="s">
-        <v>2670</v>
+        <v>2665</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>1196</v>
@@ -12555,167 +12890,167 @@
         <v>1196</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>2396</v>
+        <v>2393</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>1198</v>
       </c>
-      <c r="F13" s="145" t="s">
-        <v>2698</v>
+      <c r="F13" s="143" t="s">
+        <v>2693</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="18.75">
       <c r="A14" s="9" t="s">
-        <v>2709</v>
+        <v>2704</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>2393</v>
+        <v>2390</v>
       </c>
       <c r="C14" s="9" t="s">
+        <v>2389</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>2391</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>2392</v>
       </c>
-      <c r="D14" s="9" t="s">
-        <v>2394</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>2395</v>
-      </c>
-      <c r="F14" s="145" t="s">
-        <v>2710</v>
+      <c r="F14" s="143" t="s">
+        <v>2705</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18.75">
       <c r="A15" s="9" t="s">
-        <v>2693</v>
+        <v>2688</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>2694</v>
+        <v>2689</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>2695</v>
+        <v>2690</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>2696</v>
+        <v>2691</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>2697</v>
-      </c>
-      <c r="F15" s="145" t="s">
-        <v>2703</v>
+        <v>2692</v>
+      </c>
+      <c r="F15" s="143" t="s">
+        <v>2698</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="18.75">
       <c r="A16" s="9" t="s">
-        <v>2733</v>
+        <v>2728</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>2379</v>
+        <v>2376</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>2711</v>
+        <v>2706</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>2380</v>
+        <v>2377</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>2712</v>
-      </c>
-      <c r="F16" s="145" t="s">
-        <v>2713</v>
+        <v>2707</v>
+      </c>
+      <c r="F16" s="143" t="s">
+        <v>2708</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="18.75">
       <c r="A17" s="11" t="s">
-        <v>2469</v>
+        <v>2464</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>2484</v>
+        <v>2479</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>2491</v>
+        <v>2486</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>2486</v>
+        <v>2481</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>2492</v>
+        <v>2487</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>2485</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="155"/>
+      <c r="A18" s="148"/>
       <c r="B18"/>
       <c r="D18"/>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="155"/>
+      <c r="A19" s="148"/>
       <c r="B19"/>
       <c r="D19"/>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="155"/>
+      <c r="A20" s="148"/>
       <c r="B20"/>
       <c r="D20"/>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="155"/>
+      <c r="A21" s="148"/>
       <c r="B21"/>
       <c r="D21"/>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="155"/>
+      <c r="A22" s="148"/>
       <c r="B22"/>
       <c r="D22"/>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="155"/>
+      <c r="A23" s="148"/>
       <c r="B23"/>
       <c r="D23"/>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="155"/>
+      <c r="A24" s="148"/>
       <c r="B24"/>
       <c r="D24"/>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="155"/>
+      <c r="A25" s="148"/>
       <c r="B25"/>
       <c r="D25"/>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="155"/>
+      <c r="A26" s="148"/>
       <c r="B26"/>
       <c r="D26"/>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="155"/>
+      <c r="A27" s="148"/>
       <c r="B27"/>
       <c r="D27"/>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="155"/>
+      <c r="A28" s="148"/>
       <c r="B28"/>
       <c r="D28"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="155"/>
+      <c r="A29" s="148"/>
       <c r="B29"/>
       <c r="D29"/>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="155"/>
+      <c r="A30" s="148"/>
       <c r="B30"/>
       <c r="D30"/>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="155"/>
+      <c r="A31" s="148"/>
       <c r="B31"/>
       <c r="D31"/>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="155"/>
+      <c r="A32" s="148"/>
       <c r="B32"/>
       <c r="D32"/>
     </row>
@@ -12728,22 +13063,22 @@
       <c r="D34"/>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="155"/>
+      <c r="A35" s="148"/>
       <c r="B35"/>
       <c r="D35"/>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="155"/>
+      <c r="A36" s="148"/>
       <c r="B36"/>
       <c r="D36"/>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="156"/>
+      <c r="A37" s="149"/>
       <c r="B37"/>
       <c r="D37"/>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="156"/>
+      <c r="A38" s="149"/>
       <c r="B38"/>
       <c r="D38"/>
     </row>
@@ -12770,7 +13105,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24">
       <c r="A1" s="46" t="s">
-        <v>1954</v>
+        <v>1952</v>
       </c>
       <c r="B1" s="47" t="s">
         <v>1688</v>
@@ -12877,19 +13212,19 @@
     </row>
     <row r="7" spans="1:8" ht="18.75">
       <c r="A7" s="11" t="s">
+        <v>2133</v>
+      </c>
+      <c r="B7" s="103" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>2133</v>
+      </c>
+      <c r="D7" s="103" t="s">
+        <v>2135</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>2136</v>
-      </c>
-      <c r="B7" s="103" t="s">
-        <v>2137</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>2136</v>
-      </c>
-      <c r="D7" s="103" t="s">
-        <v>2138</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>2139</v>
       </c>
       <c r="H7" s="8"/>
     </row>
@@ -12913,19 +13248,19 @@
     </row>
     <row r="9" spans="1:8" ht="18.75">
       <c r="A9" s="11" t="s">
-        <v>2168</v>
+        <v>2165</v>
       </c>
       <c r="B9" s="103" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>2130</v>
+      </c>
+      <c r="D9" s="103" t="s">
+        <v>2131</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>2132</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>2133</v>
-      </c>
-      <c r="D9" s="103" t="s">
-        <v>2134</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>2135</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="18.75">
@@ -12933,7 +13268,7 @@
         <v>820</v>
       </c>
       <c r="B10" s="103" t="s">
-        <v>2565</v>
+        <v>2560</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>875</v>
@@ -12981,19 +13316,19 @@
     </row>
     <row r="13" spans="1:8" ht="21.75" customHeight="1">
       <c r="A13" s="16" t="s">
-        <v>2554</v>
+        <v>2549</v>
       </c>
       <c r="B13" s="101" t="s">
-        <v>2555</v>
+        <v>2550</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>2558</v>
+        <v>2553</v>
       </c>
       <c r="D13" s="101" t="s">
-        <v>2556</v>
+        <v>2551</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>2557</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="18.75">
@@ -13100,19 +13435,19 @@
     </row>
     <row r="20" spans="1:5" ht="18.75">
       <c r="A20" s="16" t="s">
-        <v>2568</v>
+        <v>2563</v>
       </c>
       <c r="B20" s="105" t="s">
-        <v>2569</v>
+        <v>2564</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>2570</v>
+        <v>2565</v>
       </c>
       <c r="D20" s="105" t="s">
-        <v>2571</v>
+        <v>2566</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>2572</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18.75">
@@ -13198,53 +13533,53 @@
     </row>
     <row r="26" spans="1:5" ht="18.75" customHeight="1">
       <c r="A26" s="11" t="s">
+        <v>2090</v>
+      </c>
+      <c r="B26" s="103" t="s">
+        <v>2091</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>2092</v>
+      </c>
+      <c r="D26" s="103" t="s">
         <v>2093</v>
       </c>
-      <c r="B26" s="103" t="s">
+      <c r="E26" s="9" t="s">
         <v>2094</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>2095</v>
-      </c>
-      <c r="D26" s="103" t="s">
-        <v>2096</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>2097</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="18.75">
       <c r="A27" s="9" t="s">
+        <v>2026</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>2027</v>
+      </c>
+      <c r="C27" s="143" t="s">
         <v>2028</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>2029</v>
-      </c>
-      <c r="C27" s="145" t="s">
-        <v>2030</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>1304</v>
       </c>
-      <c r="E27" s="145" t="s">
-        <v>2031</v>
+      <c r="E27" s="143" t="s">
+        <v>2029</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="18.75">
       <c r="A28" s="11" t="s">
+        <v>2080</v>
+      </c>
+      <c r="B28" s="103" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>2082</v>
+      </c>
+      <c r="D28" s="10" t="s">
         <v>2083</v>
       </c>
-      <c r="B28" s="103" t="s">
+      <c r="E28" s="9" t="s">
         <v>2084</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>2085</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>2086</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>2087</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="18.75">
@@ -13317,19 +13652,19 @@
     </row>
     <row r="33" spans="1:5" ht="18.75">
       <c r="A33" s="9" t="s">
-        <v>2925</v>
+        <v>2920</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>2926</v>
-      </c>
-      <c r="C33" s="145" t="s">
-        <v>2927</v>
+        <v>2921</v>
+      </c>
+      <c r="C33" s="143" t="s">
+        <v>2922</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>2928</v>
-      </c>
-      <c r="E33" s="145" t="s">
-        <v>2929</v>
+        <v>2923</v>
+      </c>
+      <c r="E33" s="143" t="s">
+        <v>2924</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="18.75">
@@ -13402,36 +13737,36 @@
     </row>
     <row r="38" spans="1:5" ht="18.75">
       <c r="A38" s="6" t="s">
+        <v>2280</v>
+      </c>
+      <c r="B38" s="101" t="s">
+        <v>2281</v>
+      </c>
+      <c r="C38" s="17" t="s">
         <v>2283</v>
       </c>
-      <c r="B38" s="101" t="s">
+      <c r="D38" s="101" t="s">
+        <v>2282</v>
+      </c>
+      <c r="E38" s="17" t="s">
         <v>2284</v>
-      </c>
-      <c r="C38" s="17" t="s">
-        <v>2286</v>
-      </c>
-      <c r="D38" s="101" t="s">
-        <v>2285</v>
-      </c>
-      <c r="E38" s="17" t="s">
-        <v>2287</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="37.5">
       <c r="A39" s="11" t="s">
+        <v>2085</v>
+      </c>
+      <c r="B39" s="103" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>2087</v>
+      </c>
+      <c r="D39" s="103" t="s">
         <v>2088</v>
       </c>
-      <c r="B39" s="103" t="s">
+      <c r="E39" s="9" t="s">
         <v>2089</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>2090</v>
-      </c>
-      <c r="D39" s="103" t="s">
-        <v>2091</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>2092</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="18.75">
@@ -13508,7 +13843,7 @@
   <sheetData>
     <row r="1" spans="1:9" s="39" customFormat="1" ht="24">
       <c r="A1" s="51" t="s">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="B1" s="110" t="s">
         <v>1672</v>
@@ -13525,19 +13860,19 @@
     </row>
     <row r="2" spans="1:9" ht="25.5" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>2192</v>
+        <v>2189</v>
       </c>
       <c r="B2" s="105" t="s">
+        <v>2194</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>2195</v>
+      </c>
+      <c r="D2" s="105" t="s">
         <v>2197</v>
       </c>
-      <c r="C2" s="17" t="s">
-        <v>2198</v>
-      </c>
-      <c r="D2" s="105" t="s">
-        <v>2200</v>
-      </c>
       <c r="E2" s="17" t="s">
-        <v>2199</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -13577,19 +13912,19 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="12" t="s">
+        <v>2174</v>
+      </c>
+      <c r="B5" s="103" t="s">
+        <v>2175</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>2176</v>
+      </c>
+      <c r="D5" s="103" t="s">
         <v>2177</v>
       </c>
-      <c r="B5" s="103" t="s">
+      <c r="E5" s="9" t="s">
         <v>2178</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>2179</v>
-      </c>
-      <c r="D5" s="103" t="s">
-        <v>2180</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>2181</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -13628,22 +13963,22 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="12" t="s">
+        <v>2169</v>
+      </c>
+      <c r="B8" s="103" t="s">
+        <v>2170</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>2171</v>
+      </c>
+      <c r="D8" s="103" t="s">
         <v>2172</v>
       </c>
-      <c r="B8" s="103" t="s">
+      <c r="E8" s="9" t="s">
         <v>2173</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>2174</v>
-      </c>
-      <c r="D8" s="103" t="s">
-        <v>2175</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>2176</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="37.5">
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="12" t="s">
         <v>811</v>
       </c>
@@ -13776,7 +14111,7 @@
     </row>
     <row r="16" spans="1:9" s="39" customFormat="1" ht="24">
       <c r="A16" s="52" t="s">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="B16" s="111" t="s">
         <v>1676</v>
@@ -13841,7 +14176,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="37.5">
+    <row r="20" spans="1:9">
       <c r="A20" s="13" t="s">
         <v>588</v>
       </c>
@@ -13962,7 +14297,7 @@
     </row>
     <row r="27" spans="1:9" s="42" customFormat="1" ht="33.75" customHeight="1">
       <c r="A27" s="53" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="B27" s="113" t="s">
         <v>89</v>
@@ -13974,19 +14309,19 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="11" t="s">
+        <v>2315</v>
+      </c>
+      <c r="B28" s="103" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>2315</v>
+      </c>
+      <c r="D28" s="103" t="s">
+        <v>2317</v>
+      </c>
+      <c r="E28" s="9" t="s">
         <v>2318</v>
-      </c>
-      <c r="B28" s="103" t="s">
-        <v>2319</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>2318</v>
-      </c>
-      <c r="D28" s="103" t="s">
-        <v>2320</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>2321</v>
       </c>
       <c r="G28" s="4"/>
     </row>
@@ -14023,30 +14358,30 @@
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="11" t="s">
+        <v>2342</v>
+      </c>
+      <c r="B31" s="103" t="s">
+        <v>2343</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>2344</v>
+      </c>
+      <c r="D31" s="101" t="s">
         <v>2345</v>
       </c>
-      <c r="B31" s="103" t="s">
+      <c r="E31" s="1" t="s">
         <v>2346</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>2347</v>
-      </c>
-      <c r="D31" s="101" t="s">
-        <v>2348</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>2349</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="11" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B32" s="103" t="s">
+        <v>1831</v>
+      </c>
+      <c r="C32" s="9" t="s">
         <v>1833</v>
-      </c>
-      <c r="B32" s="103" t="s">
-        <v>1832</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>1834</v>
       </c>
       <c r="D32" s="101"/>
       <c r="E32" s="1"/>
@@ -14116,19 +14451,19 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="11" t="s">
-        <v>2479</v>
+        <v>2474</v>
       </c>
       <c r="B37" s="103" t="s">
-        <v>2480</v>
+        <v>2475</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>2481</v>
+        <v>2476</v>
       </c>
       <c r="D37" s="103" t="s">
-        <v>2482</v>
+        <v>2477</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>2483</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -14167,13 +14502,13 @@
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="9" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>2033</v>
-      </c>
-      <c r="C40" s="145" t="s">
-        <v>2737</v>
+        <v>2031</v>
+      </c>
+      <c r="C40" s="143" t="s">
+        <v>2732</v>
       </c>
       <c r="D40" s="101"/>
       <c r="E40" s="1"/>
@@ -14197,19 +14532,19 @@
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="11" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>2191</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>2190</v>
+      </c>
+      <c r="D42" s="103" t="s">
+        <v>2192</v>
+      </c>
+      <c r="E42" s="9" t="s">
         <v>2193</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>2194</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>2193</v>
-      </c>
-      <c r="D42" s="103" t="s">
-        <v>2195</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>2196</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -14234,13 +14569,13 @@
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="6" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B44" s="101" t="s">
         <v>1844</v>
       </c>
-      <c r="B44" s="101" t="s">
+      <c r="C44" s="9" t="s">
         <v>1845</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>1846</v>
       </c>
       <c r="D44" s="101" t="s">
         <v>217</v>
@@ -14251,30 +14586,30 @@
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="9" t="s">
-        <v>2915</v>
+        <v>2910</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>2916</v>
-      </c>
-      <c r="C45" s="145" t="s">
-        <v>2917</v>
+        <v>2911</v>
+      </c>
+      <c r="C45" s="143" t="s">
+        <v>2912</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>2918</v>
-      </c>
-      <c r="E45" s="145" t="s">
-        <v>2919</v>
+        <v>2913</v>
+      </c>
+      <c r="E45" s="143" t="s">
+        <v>2914</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="11" t="s">
-        <v>2160</v>
+        <v>2157</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>2161</v>
+        <v>2158</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>2160</v>
+        <v>2157</v>
       </c>
       <c r="D46" s="103" t="s">
         <v>217</v>
@@ -14327,30 +14662,30 @@
     </row>
     <row r="49" spans="1:5" ht="37.5">
       <c r="A49" s="9" t="s">
-        <v>2924</v>
+        <v>2919</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>2930</v>
-      </c>
-      <c r="C49" s="145" t="s">
-        <v>2924</v>
+        <v>2925</v>
+      </c>
+      <c r="C49" s="143" t="s">
+        <v>2919</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>2931</v>
-      </c>
-      <c r="E49" s="145" t="s">
-        <v>2932</v>
+        <v>2926</v>
+      </c>
+      <c r="E49" s="143" t="s">
+        <v>2927</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="B50" s="101" t="s">
+        <v>1834</v>
+      </c>
+      <c r="C50" s="9" t="s">
         <v>1835</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>1836</v>
       </c>
       <c r="D50" s="101" t="s">
         <v>217</v>
@@ -14361,13 +14696,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="11" t="s">
-        <v>2065</v>
+        <v>2062</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>2066</v>
+        <v>2063</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>2067</v>
+        <v>2064</v>
       </c>
       <c r="D51" s="103" t="s">
         <v>217</v>
@@ -14378,13 +14713,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="11" t="s">
-        <v>2068</v>
+        <v>2065</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>2069</v>
+        <v>2066</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>2070</v>
+        <v>2067</v>
       </c>
       <c r="D52" s="103" t="s">
         <v>217</v>
@@ -14395,13 +14730,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B53" s="101" t="s">
         <v>1838</v>
       </c>
-      <c r="B53" s="101" t="s">
+      <c r="C53" s="9" t="s">
         <v>1839</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>1840</v>
       </c>
       <c r="D53" s="101" t="s">
         <v>217</v>
@@ -14429,13 +14764,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="B55" s="101" t="s">
+        <v>1852</v>
+      </c>
+      <c r="C55" s="9" t="s">
         <v>1853</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>1854</v>
       </c>
       <c r="D55" s="101" t="s">
         <v>217</v>
@@ -14446,36 +14781,36 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="11" t="s">
+        <v>2159</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>2160</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>2159</v>
+      </c>
+      <c r="D56" s="103" t="s">
+        <v>2161</v>
+      </c>
+      <c r="E56" s="9" t="s">
         <v>2162</v>
-      </c>
-      <c r="B56" s="10" t="s">
-        <v>2163</v>
-      </c>
-      <c r="C56" s="9" t="s">
-        <v>2162</v>
-      </c>
-      <c r="D56" s="103" t="s">
-        <v>2164</v>
-      </c>
-      <c r="E56" s="9" t="s">
-        <v>2165</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="B57" s="101" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C57" s="9" t="s">
         <v>1849</v>
       </c>
-      <c r="C57" s="9" t="s">
+      <c r="D57" s="101" t="s">
         <v>1850</v>
       </c>
-      <c r="D57" s="101" t="s">
+      <c r="E57" s="9" t="s">
         <v>1851</v>
-      </c>
-      <c r="E57" s="9" t="s">
-        <v>1852</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -14527,13 +14862,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="11" t="s">
-        <v>2071</v>
+        <v>2068</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>2072</v>
+        <v>2069</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>2073</v>
+        <v>2070</v>
       </c>
       <c r="D61" s="103" t="s">
         <v>217</v>
@@ -14578,19 +14913,19 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="9" t="s">
-        <v>2853</v>
+        <v>2848</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>2920</v>
-      </c>
-      <c r="C64" s="145" t="s">
-        <v>2921</v>
+        <v>2915</v>
+      </c>
+      <c r="C64" s="143" t="s">
+        <v>2916</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>2922</v>
-      </c>
-      <c r="E64" s="145" t="s">
-        <v>2923</v>
+        <v>2917</v>
+      </c>
+      <c r="E64" s="143" t="s">
+        <v>2918</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -14612,13 +14947,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B66" s="101" t="s">
+        <v>1840</v>
+      </c>
+      <c r="C66" s="9" t="s">
         <v>1842</v>
-      </c>
-      <c r="B66" s="101" t="s">
-        <v>1841</v>
-      </c>
-      <c r="C66" s="9" t="s">
-        <v>1843</v>
       </c>
       <c r="D66" s="101" t="s">
         <v>217</v>
@@ -14646,19 +14981,19 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
+        <v>1880</v>
+      </c>
+      <c r="B68" s="101" t="s">
         <v>1881</v>
       </c>
-      <c r="B68" s="101" t="s">
+      <c r="C68" s="9" t="s">
         <v>1882</v>
       </c>
-      <c r="C68" s="9" t="s">
+      <c r="D68" s="101" t="s">
         <v>1883</v>
       </c>
-      <c r="D68" s="101" t="s">
+      <c r="E68" s="9" t="s">
         <v>1884</v>
-      </c>
-      <c r="E68" s="9" t="s">
-        <v>1885</v>
       </c>
     </row>
   </sheetData>
@@ -14680,222 +15015,222 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.75">
       <c r="A1" s="9" t="s">
-        <v>2854</v>
+        <v>2849</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>2911</v>
+        <v>2906</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>2912</v>
+        <v>2907</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>2913</v>
+        <v>2908</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>2914</v>
-      </c>
-      <c r="F1" s="145" t="s">
-        <v>2855</v>
+        <v>2909</v>
+      </c>
+      <c r="F1" s="143" t="s">
+        <v>2850</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="18.75">
       <c r="A2" s="9" t="s">
-        <v>2864</v>
+        <v>2859</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>2908</v>
+        <v>2903</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>2908</v>
+        <v>2903</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>2909</v>
+        <v>2904</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>2909</v>
-      </c>
-      <c r="F2" s="145" t="s">
-        <v>2910</v>
+        <v>2904</v>
+      </c>
+      <c r="F2" s="143" t="s">
+        <v>2905</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="18.75">
       <c r="A3" s="9" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>2893</v>
+        <v>2888</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>2894</v>
+        <v>2889</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>2895</v>
+        <v>2890</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>2896</v>
-      </c>
-      <c r="F3" s="145" t="s">
-        <v>2897</v>
+        <v>2891</v>
+      </c>
+      <c r="F3" s="143" t="s">
+        <v>2892</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="18.75">
       <c r="A4" s="9" t="s">
-        <v>2858</v>
+        <v>2853</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>2879</v>
+        <v>2874</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>2880</v>
+        <v>2875</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>2881</v>
+        <v>2876</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>2882</v>
-      </c>
-      <c r="F4" s="145" t="s">
-        <v>2883</v>
+        <v>2877</v>
+      </c>
+      <c r="F4" s="143" t="s">
+        <v>2878</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="18.75">
       <c r="A5" s="9" t="s">
-        <v>2856</v>
+        <v>2851</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>2865</v>
+        <v>2860</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>2866</v>
+        <v>2861</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>2867</v>
+        <v>2862</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>2868</v>
-      </c>
-      <c r="F5" s="145" t="s">
-        <v>2869</v>
+        <v>2863</v>
+      </c>
+      <c r="F5" s="143" t="s">
+        <v>2864</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="56.25">
       <c r="A6" s="9" t="s">
-        <v>2859</v>
+        <v>2854</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>2884</v>
+        <v>2879</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>2885</v>
+        <v>2880</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>2886</v>
+        <v>2881</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>2885</v>
-      </c>
-      <c r="F6" s="145" t="s">
-        <v>2887</v>
+        <v>2880</v>
+      </c>
+      <c r="F6" s="143" t="s">
+        <v>2882</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18.75">
       <c r="A7" s="9" t="s">
+        <v>2868</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>2869</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>2870</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>2871</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>2872</v>
+      </c>
+      <c r="F7" s="143" t="s">
         <v>2873</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>2874</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>2875</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>2876</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>2877</v>
-      </c>
-      <c r="F7" s="145" t="s">
-        <v>2878</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="18.75">
       <c r="A8" s="9" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>2898</v>
+        <v>2893</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>2899</v>
+        <v>2894</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>2900</v>
+        <v>2895</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>2901</v>
-      </c>
-      <c r="F8" s="145" t="s">
-        <v>2902</v>
+        <v>2896</v>
+      </c>
+      <c r="F8" s="143" t="s">
+        <v>2897</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18.75">
       <c r="A9" s="9" t="s">
-        <v>2863</v>
+        <v>2858</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>2903</v>
+        <v>2898</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>2904</v>
+        <v>2899</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>2905</v>
+        <v>2900</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>2906</v>
-      </c>
-      <c r="F9" s="145" t="s">
-        <v>2907</v>
+        <v>2901</v>
+      </c>
+      <c r="F9" s="143" t="s">
+        <v>2902</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="18.75">
       <c r="A10" s="9" t="s">
-        <v>2857</v>
+        <v>2852</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>2870</v>
+        <v>2865</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>2870</v>
+        <v>2865</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>2871</v>
+        <v>2866</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>2871</v>
-      </c>
-      <c r="F10" s="145" t="s">
-        <v>2872</v>
+        <v>2866</v>
+      </c>
+      <c r="F10" s="143" t="s">
+        <v>2867</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="18.75">
       <c r="A11" s="9" t="s">
-        <v>2860</v>
+        <v>2855</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>2888</v>
+        <v>2883</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>2889</v>
+        <v>2884</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>2890</v>
+        <v>2885</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>2891</v>
-      </c>
-      <c r="F11" s="145" t="s">
-        <v>2892</v>
+        <v>2886</v>
+      </c>
+      <c r="F11" s="143" t="s">
+        <v>2887</v>
       </c>
     </row>
   </sheetData>
@@ -14918,46 +15253,46 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="59" t="s">
-        <v>2265</v>
+        <v>2262</v>
       </c>
       <c r="B1" s="117" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="C1" s="59" t="s">
-        <v>2407</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="18.75">
       <c r="A2" s="7" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="B2" s="101" t="s">
         <v>1796</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>1998</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="59" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
       <c r="B3" s="117" t="s">
-        <v>2242</v>
+        <v>2239</v>
       </c>
       <c r="C3" s="59" t="s">
-        <v>2243</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="59" t="s">
-        <v>2247</v>
+        <v>2244</v>
       </c>
       <c r="B4" s="117" t="s">
-        <v>2248</v>
+        <v>2245</v>
       </c>
       <c r="C4" s="59" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18.75">
@@ -14968,18 +15303,18 @@
         <v>1795</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30">
       <c r="A6" s="59" t="s">
-        <v>2244</v>
+        <v>2241</v>
       </c>
       <c r="B6" s="117" t="s">
-        <v>2245</v>
+        <v>2242</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="18.75">
@@ -14990,7 +15325,7 @@
         <v>1798</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="18.75">
@@ -15001,18 +15336,18 @@
         <v>1790</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="59" t="s">
-        <v>2250</v>
+        <v>2247</v>
       </c>
       <c r="B9" s="119" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="C9" s="59" t="s">
-        <v>2269</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="18.75">
@@ -15023,29 +15358,29 @@
         <v>1786</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30">
       <c r="A11" s="59" t="s">
-        <v>2267</v>
+        <v>2264</v>
       </c>
       <c r="B11" s="117" t="s">
-        <v>2251</v>
+        <v>2248</v>
       </c>
       <c r="C11" s="59" t="s">
-        <v>2252</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="59" t="s">
-        <v>2259</v>
+        <v>2256</v>
       </c>
       <c r="B12" s="117" t="s">
-        <v>2260</v>
+        <v>2257</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>2261</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="18.75">
@@ -15061,90 +15396,90 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="59" t="s">
-        <v>2253</v>
+        <v>2250</v>
       </c>
       <c r="B14" s="117" t="s">
-        <v>2254</v>
+        <v>2251</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>2255</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="59" t="s">
-        <v>2256</v>
+        <v>2253</v>
       </c>
       <c r="B15" s="117" t="s">
-        <v>2257</v>
+        <v>2254</v>
       </c>
       <c r="C15" s="59" t="s">
-        <v>2258</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="7" t="s">
-        <v>2351</v>
+        <v>2348</v>
       </c>
       <c r="B16" s="119" t="s">
-        <v>2350</v>
+        <v>2347</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>2352</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="18.75">
       <c r="A17" s="7" t="s">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="B17" s="101" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="59" t="s">
-        <v>2272</v>
+        <v>2269</v>
       </c>
       <c r="B18" s="119" t="s">
-        <v>2273</v>
+        <v>2270</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="7" t="s">
-        <v>2622</v>
+        <v>2617</v>
       </c>
       <c r="B19" s="140" t="s">
-        <v>2621</v>
+        <v>2616</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>2620</v>
+        <v>2615</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="7" t="s">
-        <v>2364</v>
+        <v>2361</v>
       </c>
       <c r="B20" s="119" t="s">
-        <v>2366</v>
+        <v>2363</v>
       </c>
       <c r="C20" s="59" t="s">
-        <v>2365</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="7" t="s">
-        <v>2404</v>
+        <v>2401</v>
       </c>
       <c r="B21" s="119" t="s">
-        <v>2405</v>
+        <v>2402</v>
       </c>
       <c r="C21" s="59" t="s">
-        <v>2406</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="18.75">
@@ -15155,18 +15490,18 @@
         <v>1800</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="18.75">
       <c r="A23" s="7" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="B23" s="118" t="s">
         <v>1797</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="18.75">
@@ -15177,40 +15512,40 @@
         <v>1799</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="21.75" customHeight="1">
       <c r="A25" s="59" t="s">
-        <v>2262</v>
+        <v>2259</v>
       </c>
       <c r="B25" s="117" t="s">
-        <v>2263</v>
+        <v>2260</v>
       </c>
       <c r="C25" s="59" t="s">
-        <v>2264</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="59" t="s">
-        <v>2240</v>
+        <v>2237</v>
       </c>
       <c r="B26" s="117" t="s">
-        <v>2270</v>
+        <v>2267</v>
       </c>
       <c r="C26" s="59" t="s">
-        <v>2271</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="7" t="s">
-        <v>2315</v>
+        <v>2312</v>
       </c>
       <c r="B27" s="119" t="s">
-        <v>2317</v>
+        <v>2314</v>
       </c>
       <c r="C27" s="59" t="s">
-        <v>2316</v>
+        <v>2313</v>
       </c>
     </row>
   </sheetData>
@@ -15812,7 +16147,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="41" customFormat="1" ht="24">
       <c r="A1" s="55" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="B1" s="126" t="s">
         <v>1703</v>
@@ -16069,7 +16404,7 @@
         <v>1430</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>2397</v>
+        <v>2394</v>
       </c>
       <c r="D20" s="31"/>
       <c r="E20" s="1"/>
@@ -16082,7 +16417,7 @@
         <v>1432</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>2398</v>
+        <v>2395</v>
       </c>
       <c r="D21" s="31" t="s">
         <v>1433</v>
@@ -16093,112 +16428,112 @@
     </row>
     <row r="22" spans="1:5" ht="56.25">
       <c r="A22" s="11" t="s">
+        <v>2005</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>2006</v>
+      </c>
+      <c r="C22" s="9" t="s">
         <v>2007</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>2008</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>2009</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="37.5">
       <c r="A23" s="11" t="s">
+        <v>2008</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>2009</v>
+      </c>
+      <c r="C23" s="9" t="s">
         <v>2010</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>2011</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="21.75" customHeight="1">
       <c r="A24" s="11" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>2012</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>2013</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>2014</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>2015</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="37.5">
       <c r="A25" s="11" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>2015</v>
+      </c>
+      <c r="C25" s="9" t="s">
         <v>2016</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>2017</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>2018</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="56.25">
       <c r="A26" s="11" t="s">
+        <v>2017</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>2018</v>
+      </c>
+      <c r="C26" s="9" t="s">
         <v>2019</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>2020</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>2021</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="37.5">
       <c r="A27" s="11" t="s">
+        <v>2020</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>2021</v>
+      </c>
+      <c r="C27" s="9" t="s">
         <v>2022</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>2023</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>2024</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="37.5">
       <c r="A28" s="11" t="s">
+        <v>2023</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>2024</v>
+      </c>
+      <c r="C28" s="9" t="s">
         <v>2025</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>2026</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>2027</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="18.75">
       <c r="A29" s="14" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="B29" s="101" t="s">
+        <v>1824</v>
+      </c>
+      <c r="C29" s="31" t="s">
         <v>1825</v>
-      </c>
-      <c r="C29" s="31" t="s">
-        <v>1826</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="18.75">
       <c r="A30" s="14" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="B30" s="101" t="s">
+        <v>1826</v>
+      </c>
+      <c r="C30" s="31" t="s">
         <v>1827</v>
-      </c>
-      <c r="C30" s="31" t="s">
-        <v>1828</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="18.75">
       <c r="A31" s="14" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="B31" s="101" t="s">
+        <v>1828</v>
+      </c>
+      <c r="C31" s="31" t="s">
         <v>1829</v>
-      </c>
-      <c r="C31" s="31" t="s">
-        <v>1830</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="18.75">
@@ -16209,12 +16544,12 @@
         <v>191</v>
       </c>
       <c r="C32" s="31" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="24">
       <c r="A33" s="48" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="B33" s="48" t="s">
         <v>1704</v>
@@ -16275,7 +16610,7 @@
     </row>
     <row r="38" spans="1:5" ht="48">
       <c r="A38" s="57" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="B38" s="129" t="s">
         <v>1303</v>
@@ -16331,10 +16666,10 @@
       <c r="B41" s="105" t="s">
         <v>536</v>
       </c>
-      <c r="C41" s="143" t="s">
+      <c r="C41" s="154" t="s">
         <v>559</v>
       </c>
-      <c r="D41" s="144"/>
+      <c r="D41" s="155"/>
       <c r="E41" s="71" t="s">
         <v>217</v>
       </c>
@@ -16375,13 +16710,13 @@
     </row>
     <row r="44" spans="1:5" ht="56.25">
       <c r="A44" s="15" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="B44" s="105" t="s">
         <v>539</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>2289</v>
+        <v>2286</v>
       </c>
       <c r="D44" s="105" t="s">
         <v>217</v>
@@ -16392,24 +16727,24 @@
     </row>
     <row r="45" spans="1:5" ht="37.5">
       <c r="A45" s="11" t="s">
+        <v>2071</v>
+      </c>
+      <c r="B45" s="103" t="s">
+        <v>2072</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>2073</v>
+      </c>
+      <c r="D45" s="103" t="s">
         <v>2074</v>
       </c>
-      <c r="B45" s="103" t="s">
+      <c r="E45" s="9" t="s">
         <v>2075</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>2076</v>
-      </c>
-      <c r="D45" s="103" t="s">
-        <v>2077</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>2078</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="18.75">
       <c r="A46" s="6" t="s">
-        <v>2399</v>
+        <v>2396</v>
       </c>
       <c r="B46" s="106" t="s">
         <v>1265</v>
@@ -16418,20 +16753,20 @@
         <v>1262</v>
       </c>
       <c r="D46" s="133" t="s">
-        <v>2401</v>
+        <v>2398</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="37.5">
       <c r="A47" s="6" t="s">
-        <v>2400</v>
+        <v>2397</v>
       </c>
       <c r="B47" s="106"/>
       <c r="C47" s="1"/>
       <c r="D47" s="133" t="s">
-        <v>2402</v>
+        <v>2399</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>1435</v>
@@ -16472,13 +16807,13 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="9" t="s">
-        <v>2403</v>
+        <v>2400</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>2738</v>
-      </c>
-      <c r="C1" s="145" t="s">
-        <v>2739</v>
+        <v>2733</v>
+      </c>
+      <c r="C1" s="143" t="s">
+        <v>2734</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -16486,10 +16821,10 @@
         <v>168</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>2740</v>
-      </c>
-      <c r="C2" s="145" t="s">
-        <v>2741</v>
+        <v>2735</v>
+      </c>
+      <c r="C2" s="143" t="s">
+        <v>2736</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -16497,10 +16832,10 @@
         <v>169</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>2742</v>
-      </c>
-      <c r="C3" s="145" t="s">
-        <v>2743</v>
+        <v>2737</v>
+      </c>
+      <c r="C3" s="143" t="s">
+        <v>2738</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -16508,10 +16843,10 @@
         <v>170</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>2744</v>
-      </c>
-      <c r="C4" s="145" t="s">
-        <v>2745</v>
+        <v>2739</v>
+      </c>
+      <c r="C4" s="143" t="s">
+        <v>2740</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -16519,10 +16854,10 @@
         <v>171</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>2746</v>
-      </c>
-      <c r="C5" s="145" t="s">
-        <v>2747</v>
+        <v>2741</v>
+      </c>
+      <c r="C5" s="143" t="s">
+        <v>2742</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -16530,9 +16865,9 @@
         <v>392</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>2748</v>
-      </c>
-      <c r="C6" s="145" t="s">
+        <v>2743</v>
+      </c>
+      <c r="C6" s="143" t="s">
         <v>206</v>
       </c>
       <c r="H6" s="2" t="s">
@@ -16541,13 +16876,13 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="9" t="s">
-        <v>2082</v>
+        <v>2079</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>2749</v>
-      </c>
-      <c r="C7" s="145" t="s">
-        <v>2750</v>
+        <v>2744</v>
+      </c>
+      <c r="C7" s="143" t="s">
+        <v>2745</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -16555,10 +16890,10 @@
         <v>172</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>2751</v>
-      </c>
-      <c r="C8" s="145" t="s">
-        <v>2752</v>
+        <v>2746</v>
+      </c>
+      <c r="C8" s="143" t="s">
+        <v>2747</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -16566,10 +16901,10 @@
         <v>173</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>2753</v>
-      </c>
-      <c r="C9" s="145" t="s">
-        <v>2754</v>
+        <v>2748</v>
+      </c>
+      <c r="C9" s="143" t="s">
+        <v>2749</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -16577,10 +16912,10 @@
         <v>174</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>2755</v>
-      </c>
-      <c r="C10" s="145" t="s">
-        <v>2756</v>
+        <v>2750</v>
+      </c>
+      <c r="C10" s="143" t="s">
+        <v>2751</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -16588,10 +16923,10 @@
         <v>176</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>2757</v>
-      </c>
-      <c r="C11" s="145" t="s">
-        <v>2758</v>
+        <v>2752</v>
+      </c>
+      <c r="C11" s="143" t="s">
+        <v>2753</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -16599,9 +16934,9 @@
         <v>177</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>2759</v>
-      </c>
-      <c r="C12" s="145" t="s">
+        <v>2754</v>
+      </c>
+      <c r="C12" s="143" t="s">
         <v>258</v>
       </c>
     </row>
@@ -16610,10 +16945,10 @@
         <v>243</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>2760</v>
-      </c>
-      <c r="C13" s="145" t="s">
-        <v>2761</v>
+        <v>2755</v>
+      </c>
+      <c r="C13" s="143" t="s">
+        <v>2756</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -16623,7 +16958,7 @@
       <c r="B14" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="C14" s="145" t="s">
+      <c r="C14" s="143" t="s">
         <v>180</v>
       </c>
     </row>
@@ -16632,10 +16967,10 @@
         <v>1375</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>2762</v>
-      </c>
-      <c r="C15" s="145" t="s">
-        <v>2763</v>
+        <v>2757</v>
+      </c>
+      <c r="C15" s="143" t="s">
+        <v>2758</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -16643,10 +16978,10 @@
         <v>1376</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>2764</v>
-      </c>
-      <c r="C16" s="145" t="s">
-        <v>2765</v>
+        <v>2759</v>
+      </c>
+      <c r="C16" s="143" t="s">
+        <v>2760</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -16654,10 +16989,10 @@
         <v>181</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>2766</v>
-      </c>
-      <c r="C17" s="145" t="s">
-        <v>2767</v>
+        <v>2761</v>
+      </c>
+      <c r="C17" s="143" t="s">
+        <v>2762</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -16665,32 +17000,32 @@
         <v>1378</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>2768</v>
-      </c>
-      <c r="C18" s="145" t="s">
-        <v>2769</v>
+        <v>2763</v>
+      </c>
+      <c r="C18" s="143" t="s">
+        <v>2764</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="9" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>2770</v>
-      </c>
-      <c r="C19" s="145" t="s">
-        <v>2771</v>
+        <v>2765</v>
+      </c>
+      <c r="C19" s="143" t="s">
+        <v>2766</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="9" t="s">
-        <v>2619</v>
+        <v>2614</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>2772</v>
-      </c>
-      <c r="C20" s="145" t="s">
-        <v>2773</v>
+        <v>2767</v>
+      </c>
+      <c r="C20" s="143" t="s">
+        <v>2768</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -16698,10 +17033,10 @@
         <v>182</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>2774</v>
-      </c>
-      <c r="C21" s="145" t="s">
-        <v>2775</v>
+        <v>2769</v>
+      </c>
+      <c r="C21" s="143" t="s">
+        <v>2770</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -16709,21 +17044,21 @@
         <v>183</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>2776</v>
-      </c>
-      <c r="C22" s="145" t="s">
-        <v>2777</v>
+        <v>2771</v>
+      </c>
+      <c r="C22" s="143" t="s">
+        <v>2772</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="9" t="s">
-        <v>2778</v>
+        <v>2773</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="C23" s="145" t="s">
-        <v>2779</v>
+      <c r="C23" s="143" t="s">
+        <v>2774</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -16733,8 +17068,8 @@
       <c r="B24" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="C24" s="145" t="s">
-        <v>2780</v>
+      <c r="C24" s="143" t="s">
+        <v>2775</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -16742,10 +17077,10 @@
         <v>192</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>2781</v>
-      </c>
-      <c r="C25" s="145" t="s">
-        <v>2782</v>
+        <v>2776</v>
+      </c>
+      <c r="C25" s="143" t="s">
+        <v>2777</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -16753,21 +17088,21 @@
         <v>393</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>2783</v>
-      </c>
-      <c r="C26" s="145" t="s">
-        <v>2784</v>
+        <v>2778</v>
+      </c>
+      <c r="C26" s="143" t="s">
+        <v>2779</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="9" t="s">
-        <v>2416</v>
+        <v>2413</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>2785</v>
-      </c>
-      <c r="C27" s="145" t="s">
-        <v>2786</v>
+        <v>2780</v>
+      </c>
+      <c r="C27" s="143" t="s">
+        <v>2781</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -16775,21 +17110,21 @@
         <v>796</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>2787</v>
-      </c>
-      <c r="C28" s="145" t="s">
-        <v>2788</v>
+        <v>2782</v>
+      </c>
+      <c r="C28" s="143" t="s">
+        <v>2783</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="9" t="s">
-        <v>2789</v>
+        <v>2784</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>2790</v>
-      </c>
-      <c r="C29" s="145" t="s">
-        <v>2791</v>
+        <v>2785</v>
+      </c>
+      <c r="C29" s="143" t="s">
+        <v>2786</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -16797,21 +17132,21 @@
         <v>193</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>2792</v>
-      </c>
-      <c r="C30" s="145" t="s">
-        <v>2793</v>
+        <v>2787</v>
+      </c>
+      <c r="C30" s="143" t="s">
+        <v>2788</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="9" t="s">
-        <v>2275</v>
+        <v>2272</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>2794</v>
-      </c>
-      <c r="C31" s="145" t="s">
-        <v>2795</v>
+        <v>2789</v>
+      </c>
+      <c r="C31" s="143" t="s">
+        <v>2790</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -16819,32 +17154,32 @@
         <v>194</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>2796</v>
-      </c>
-      <c r="C32" s="145" t="s">
-        <v>2797</v>
+        <v>2791</v>
+      </c>
+      <c r="C32" s="143" t="s">
+        <v>2792</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="9" t="s">
-        <v>2625</v>
+        <v>2620</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>2798</v>
-      </c>
-      <c r="C33" s="145" t="s">
-        <v>2799</v>
+        <v>2793</v>
+      </c>
+      <c r="C33" s="143" t="s">
+        <v>2794</v>
       </c>
     </row>
     <row r="34" spans="1:4" customFormat="1">
       <c r="A34" s="9" t="s">
-        <v>2628</v>
+        <v>2623</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>2800</v>
-      </c>
-      <c r="C34" s="145" t="s">
-        <v>2801</v>
+        <v>2795</v>
+      </c>
+      <c r="C34" s="143" t="s">
+        <v>2796</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>217</v>
@@ -16852,24 +17187,24 @@
     </row>
     <row r="35" spans="1:4" ht="37.5">
       <c r="A35" s="9" t="s">
-        <v>2626</v>
+        <v>2621</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>2802</v>
-      </c>
-      <c r="C35" s="145" t="s">
-        <v>2803</v>
+        <v>2797</v>
+      </c>
+      <c r="C35" s="143" t="s">
+        <v>2798</v>
       </c>
     </row>
     <row r="36" spans="1:4" customFormat="1" ht="37.5">
       <c r="A36" s="9" t="s">
-        <v>2627</v>
+        <v>2622</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>2804</v>
-      </c>
-      <c r="C36" s="145" t="s">
-        <v>2805</v>
+        <v>2799</v>
+      </c>
+      <c r="C36" s="143" t="s">
+        <v>2800</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -16877,54 +17212,54 @@
         <v>244</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>2806</v>
-      </c>
-      <c r="C37" s="145" t="s">
-        <v>2807</v>
+        <v>2801</v>
+      </c>
+      <c r="C37" s="143" t="s">
+        <v>2802</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="9" t="s">
-        <v>2167</v>
+        <v>2164</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>2808</v>
-      </c>
-      <c r="C38" s="145" t="s">
-        <v>2809</v>
+        <v>2803</v>
+      </c>
+      <c r="C38" s="143" t="s">
+        <v>2804</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="9" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>2810</v>
-      </c>
-      <c r="C39" s="145" t="s">
-        <v>2811</v>
+        <v>2805</v>
+      </c>
+      <c r="C39" s="143" t="s">
+        <v>2806</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="9" t="s">
-        <v>2156</v>
+        <v>2153</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>2812</v>
-      </c>
-      <c r="C40" s="145" t="s">
-        <v>2813</v>
+        <v>2807</v>
+      </c>
+      <c r="C40" s="143" t="s">
+        <v>2808</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="9" t="s">
-        <v>2081</v>
+        <v>2078</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>2814</v>
-      </c>
-      <c r="C41" s="145" t="s">
-        <v>2815</v>
+        <v>2809</v>
+      </c>
+      <c r="C41" s="143" t="s">
+        <v>2810</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -16934,7 +17269,7 @@
       <c r="B42" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="C42" s="145" t="s">
+      <c r="C42" s="143" t="s">
         <v>206</v>
       </c>
     </row>
@@ -16943,10 +17278,10 @@
         <v>1377</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>2816</v>
-      </c>
-      <c r="C43" s="145" t="s">
-        <v>2817</v>
+        <v>2811</v>
+      </c>
+      <c r="C43" s="143" t="s">
+        <v>2812</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="24.75" customHeight="1">
@@ -16954,10 +17289,10 @@
         <v>207</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>2834</v>
-      </c>
-      <c r="C44" s="145" t="s">
-        <v>2835</v>
+        <v>2829</v>
+      </c>
+      <c r="C44" s="143" t="s">
+        <v>2830</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -16967,8 +17302,8 @@
       <c r="B45" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="C45" s="145" t="s">
-        <v>2818</v>
+      <c r="C45" s="143" t="s">
+        <v>2813</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -16976,10 +17311,10 @@
         <v>210</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>2819</v>
-      </c>
-      <c r="C46" s="145" t="s">
-        <v>2820</v>
+        <v>2814</v>
+      </c>
+      <c r="C46" s="143" t="s">
+        <v>2815</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -16987,10 +17322,10 @@
         <v>213</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>2821</v>
-      </c>
-      <c r="C47" s="145" t="s">
-        <v>2822</v>
+        <v>2816</v>
+      </c>
+      <c r="C47" s="143" t="s">
+        <v>2817</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -16998,21 +17333,21 @@
         <v>211</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>2823</v>
-      </c>
-      <c r="C48" s="145" t="s">
-        <v>2824</v>
+        <v>2818</v>
+      </c>
+      <c r="C48" s="143" t="s">
+        <v>2819</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="17.25" customHeight="1">
       <c r="A49" s="9" t="s">
-        <v>2825</v>
+        <v>2820</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>2826</v>
-      </c>
-      <c r="C49" s="145" t="s">
-        <v>2827</v>
+        <v>2821</v>
+      </c>
+      <c r="C49" s="143" t="s">
+        <v>2822</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -17020,10 +17355,10 @@
         <v>212</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>2828</v>
-      </c>
-      <c r="C50" s="145" t="s">
-        <v>2829</v>
+        <v>2823</v>
+      </c>
+      <c r="C50" s="143" t="s">
+        <v>2824</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -17031,10 +17366,10 @@
         <v>214</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>2830</v>
-      </c>
-      <c r="C51" s="145" t="s">
-        <v>2831</v>
+        <v>2825</v>
+      </c>
+      <c r="C51" s="143" t="s">
+        <v>2826</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -17042,120 +17377,120 @@
         <v>215</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>2832</v>
-      </c>
-      <c r="C52" s="145" t="s">
-        <v>2833</v>
+        <v>2827</v>
+      </c>
+      <c r="C52" s="143" t="s">
+        <v>2828</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="9" t="s">
-        <v>2668</v>
-      </c>
-      <c r="B53" s="152" t="s">
-        <v>2646</v>
-      </c>
-      <c r="C53" s="145" t="s">
-        <v>2647</v>
+        <v>2663</v>
+      </c>
+      <c r="B53" s="146" t="s">
+        <v>2641</v>
+      </c>
+      <c r="C53" s="143" t="s">
+        <v>2642</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="9" t="s">
-        <v>2648</v>
-      </c>
-      <c r="B54" s="152" t="s">
-        <v>2649</v>
-      </c>
-      <c r="C54" s="145" t="s">
-        <v>2650</v>
+        <v>2643</v>
+      </c>
+      <c r="B54" s="146" t="s">
+        <v>2644</v>
+      </c>
+      <c r="C54" s="143" t="s">
+        <v>2645</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="9" t="s">
-        <v>2651</v>
-      </c>
-      <c r="B55" s="152" t="s">
-        <v>2652</v>
-      </c>
-      <c r="C55" s="145" t="s">
-        <v>2653</v>
+        <v>2646</v>
+      </c>
+      <c r="B55" s="146" t="s">
+        <v>2647</v>
+      </c>
+      <c r="C55" s="143" t="s">
+        <v>2648</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="9" t="s">
-        <v>2641</v>
-      </c>
-      <c r="B56" s="152" t="s">
-        <v>2654</v>
-      </c>
-      <c r="C56" s="145" t="s">
-        <v>2655</v>
+        <v>2636</v>
+      </c>
+      <c r="B56" s="146" t="s">
+        <v>2649</v>
+      </c>
+      <c r="C56" s="143" t="s">
+        <v>2650</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="9" t="s">
-        <v>2642</v>
-      </c>
-      <c r="B57" s="152" t="s">
-        <v>2656</v>
-      </c>
-      <c r="C57" s="145" t="s">
-        <v>2657</v>
+        <v>2637</v>
+      </c>
+      <c r="B57" s="146" t="s">
+        <v>2651</v>
+      </c>
+      <c r="C57" s="143" t="s">
+        <v>2652</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="9" t="s">
-        <v>2643</v>
-      </c>
-      <c r="B58" s="152" t="s">
-        <v>2658</v>
-      </c>
-      <c r="C58" s="145" t="s">
-        <v>2659</v>
+        <v>2638</v>
+      </c>
+      <c r="B58" s="146" t="s">
+        <v>2653</v>
+      </c>
+      <c r="C58" s="143" t="s">
+        <v>2654</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="9" t="s">
-        <v>2660</v>
-      </c>
-      <c r="B59" s="152" t="s">
-        <v>2661</v>
-      </c>
-      <c r="C59" s="145" t="s">
-        <v>2662</v>
+        <v>2655</v>
+      </c>
+      <c r="B59" s="146" t="s">
+        <v>2656</v>
+      </c>
+      <c r="C59" s="143" t="s">
+        <v>2657</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="9" t="s">
-        <v>2663</v>
-      </c>
-      <c r="B60" s="152" t="s">
-        <v>2664</v>
-      </c>
-      <c r="C60" s="145" t="s">
-        <v>2665</v>
+        <v>2658</v>
+      </c>
+      <c r="B60" s="146" t="s">
+        <v>2659</v>
+      </c>
+      <c r="C60" s="143" t="s">
+        <v>2660</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="9" t="s">
-        <v>2644</v>
-      </c>
-      <c r="B61" s="152" t="s">
-        <v>2666</v>
-      </c>
-      <c r="C61" s="145" t="s">
+        <v>2639</v>
+      </c>
+      <c r="B61" s="146" t="s">
+        <v>2661</v>
+      </c>
+      <c r="C61" s="143" t="s">
         <v>933</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="9" t="s">
-        <v>2645</v>
-      </c>
-      <c r="B62" s="152" t="s">
+        <v>2640</v>
+      </c>
+      <c r="B62" s="146" t="s">
         <v>938</v>
       </c>
-      <c r="C62" s="145" t="s">
-        <v>2667</v>
+      <c r="C62" s="143" t="s">
+        <v>2662</v>
       </c>
     </row>
   </sheetData>
@@ -17190,68 +17525,68 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="11" t="s">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="B2" s="103" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="11" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="B3" s="103" t="s">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="11" t="s">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="B4" s="103" t="s">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="11" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="B5" s="103" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>1980</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="11" t="s">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="B6" s="103" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>1973</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="11" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="B7" s="103" t="s">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -17267,46 +17602,46 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="11" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="B9" s="103" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="11" t="s">
+        <v>1972</v>
+      </c>
+      <c r="B10" s="103" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>1974</v>
-      </c>
-      <c r="B10" s="103" t="s">
-        <v>1975</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>1976</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="11" t="s">
+        <v>1986</v>
+      </c>
+      <c r="B11" s="103" t="s">
+        <v>1987</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>1988</v>
-      </c>
-      <c r="B11" s="103" t="s">
-        <v>1989</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>1990</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="37.5">
       <c r="A12" s="11" t="s">
+        <v>1983</v>
+      </c>
+      <c r="B12" s="103" t="s">
+        <v>1984</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>1985</v>
-      </c>
-      <c r="B12" s="103" t="s">
-        <v>1986</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>1987</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -17479,7 +17814,7 @@
         <v>249</v>
       </c>
       <c r="B28" s="101" t="s">
-        <v>2311</v>
+        <v>2308</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>248</v>
@@ -17587,22 +17922,22 @@
     </row>
     <row r="5" spans="1:6" ht="18.75">
       <c r="A5" s="142" t="s">
-        <v>2234</v>
+        <v>2231</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>2170</v>
+        <v>2167</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>2171</v>
+        <v>2168</v>
       </c>
       <c r="D5" s="65" t="s">
-        <v>2231</v>
+        <v>2228</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>2233</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="18.75">
@@ -17687,22 +18022,22 @@
     </row>
     <row r="10" spans="1:6" ht="18.75">
       <c r="A10" s="11" t="s">
-        <v>2580</v>
+        <v>2575</v>
       </c>
       <c r="B10" s="141" t="s">
-        <v>2586</v>
+        <v>2581</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>2587</v>
+        <v>2582</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>2588</v>
+        <v>2583</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>2589</v>
+        <v>2584</v>
       </c>
       <c r="F10" s="59" t="s">
-        <v>2590</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="18.75">
@@ -17767,22 +18102,22 @@
     </row>
     <row r="14" spans="1:6" ht="18.75">
       <c r="A14" s="60" t="s">
-        <v>2080</v>
+        <v>2077</v>
       </c>
       <c r="B14" s="21" t="s">
+        <v>2223</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>2224</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E14" s="35" t="s">
         <v>2226</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="F14" s="10" t="s">
         <v>2227</v>
-      </c>
-      <c r="D14" s="28" t="s">
-        <v>2228</v>
-      </c>
-      <c r="E14" s="35" t="s">
-        <v>2229</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>2230</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18.75">
@@ -17847,22 +18182,22 @@
     </row>
     <row r="18" spans="1:6" ht="18.75">
       <c r="A18" s="9" t="s">
+        <v>2604</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>2605</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>2606</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>2607</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>2608</v>
+      </c>
+      <c r="F18" s="9" t="s">
         <v>2609</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>2610</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>2611</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>2612</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>2613</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>2614</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="18.75">
@@ -17947,22 +18282,22 @@
     </row>
     <row r="23" spans="1:6" ht="18.75">
       <c r="A23" s="60" t="s">
+        <v>2574</v>
+      </c>
+      <c r="B23" s="62" t="s">
+        <v>2596</v>
+      </c>
+      <c r="C23" s="64" t="s">
+        <v>2578</v>
+      </c>
+      <c r="D23" s="66" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E23" s="68" t="s">
         <v>2579</v>
       </c>
-      <c r="B23" s="62" t="s">
-        <v>2601</v>
-      </c>
-      <c r="C23" s="64" t="s">
-        <v>2583</v>
-      </c>
-      <c r="D23" s="66" t="s">
-        <v>2602</v>
-      </c>
-      <c r="E23" s="68" t="s">
-        <v>2584</v>
-      </c>
       <c r="F23" s="59" t="s">
-        <v>2585</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="18.75">
@@ -18007,62 +18342,62 @@
     </row>
     <row r="26" spans="1:6" ht="18.75">
       <c r="A26" s="60" t="s">
-        <v>2582</v>
+        <v>2577</v>
       </c>
       <c r="B26" s="62" t="s">
-        <v>2596</v>
+        <v>2591</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>2597</v>
+        <v>2592</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>2598</v>
+        <v>2593</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>2599</v>
+        <v>2594</v>
       </c>
       <c r="F26" s="59" t="s">
-        <v>2600</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="18.75">
       <c r="A27" s="60" t="s">
-        <v>2079</v>
+        <v>2076</v>
       </c>
       <c r="B27" s="61" t="s">
+        <v>2218</v>
+      </c>
+      <c r="C27" s="63" t="s">
+        <v>2219</v>
+      </c>
+      <c r="D27" s="65" t="s">
+        <v>2220</v>
+      </c>
+      <c r="E27" s="67" t="s">
         <v>2221</v>
       </c>
-      <c r="C27" s="63" t="s">
+      <c r="F27" s="10" t="s">
         <v>2222</v>
-      </c>
-      <c r="D27" s="65" t="s">
-        <v>2223</v>
-      </c>
-      <c r="E27" s="67" t="s">
-        <v>2224</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>2225</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="18.75">
       <c r="A28" s="11" t="s">
-        <v>2498</v>
+        <v>2493</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>2493</v>
+        <v>2488</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>2494</v>
+        <v>2489</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>2495</v>
+        <v>2490</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>2496</v>
+        <v>2491</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>2497</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="18.75">
@@ -18207,42 +18542,42 @@
     </row>
     <row r="36" spans="1:11" ht="18.75">
       <c r="A36" s="9" t="s">
+        <v>2598</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>2599</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>2600</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>2601</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>2602</v>
+      </c>
+      <c r="F36" s="9" t="s">
         <v>2603</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>2604</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>2605</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>2606</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>2607</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>2608</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="18.75">
       <c r="A37" s="60" t="s">
-        <v>2581</v>
+        <v>2576</v>
       </c>
       <c r="B37" s="62" t="s">
-        <v>2591</v>
+        <v>2586</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>2592</v>
+        <v>2587</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>2593</v>
+        <v>2588</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>2594</v>
+        <v>2589</v>
       </c>
       <c r="F37" s="59" t="s">
-        <v>2595</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="18.75">
@@ -18296,7 +18631,7 @@
         <v>1389</v>
       </c>
       <c r="D40" s="36" t="s">
-        <v>2312</v>
+        <v>2309</v>
       </c>
       <c r="E40" s="35" t="s">
         <v>1390</v>
@@ -18307,22 +18642,22 @@
     </row>
     <row r="41" spans="1:11" ht="18.75">
       <c r="A41" s="11" t="s">
+        <v>1874</v>
+      </c>
+      <c r="B41" s="24" t="s">
         <v>1875</v>
       </c>
-      <c r="B41" s="24" t="s">
+      <c r="C41" s="27" t="s">
         <v>1876</v>
       </c>
-      <c r="C41" s="27" t="s">
+      <c r="D41" s="36" t="s">
         <v>1877</v>
       </c>
-      <c r="D41" s="36" t="s">
+      <c r="E41" s="35" t="s">
         <v>1878</v>
       </c>
-      <c r="E41" s="35" t="s">
+      <c r="F41" s="9" t="s">
         <v>1879</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>1880</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="18" customHeight="1">
@@ -18347,22 +18682,22 @@
     </row>
     <row r="43" spans="1:11" ht="18.75">
       <c r="A43" s="11" t="s">
-        <v>2623</v>
+        <v>2618</v>
       </c>
       <c r="B43" s="24" t="s">
+        <v>2385</v>
+      </c>
+      <c r="C43" s="27" t="s">
+        <v>2387</v>
+      </c>
+      <c r="D43" s="36" t="s">
         <v>2388</v>
-      </c>
-      <c r="C43" s="27" t="s">
-        <v>2390</v>
-      </c>
-      <c r="D43" s="36" t="s">
-        <v>2391</v>
       </c>
       <c r="E43" s="35" t="s">
         <v>827</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>2389</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="18.75">
@@ -18433,22 +18768,22 @@
     </row>
     <row r="47" spans="1:11" ht="18.75">
       <c r="A47" s="60" t="s">
+        <v>2554</v>
+      </c>
+      <c r="B47" s="62" t="s">
+        <v>2555</v>
+      </c>
+      <c r="C47" s="64" t="s">
+        <v>2556</v>
+      </c>
+      <c r="D47" s="66" t="s">
+        <v>2557</v>
+      </c>
+      <c r="E47" s="68" t="s">
+        <v>2558</v>
+      </c>
+      <c r="F47" s="10" t="s">
         <v>2559</v>
-      </c>
-      <c r="B47" s="62" t="s">
-        <v>2560</v>
-      </c>
-      <c r="C47" s="64" t="s">
-        <v>2561</v>
-      </c>
-      <c r="D47" s="66" t="s">
-        <v>2562</v>
-      </c>
-      <c r="E47" s="68" t="s">
-        <v>2563</v>
-      </c>
-      <c r="F47" s="10" t="s">
-        <v>2564</v>
       </c>
       <c r="H47" s="8"/>
     </row>
@@ -18474,22 +18809,22 @@
     </row>
     <row r="49" spans="1:6" ht="18.75">
       <c r="A49" s="60" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
       <c r="B49" s="62" t="s">
+        <v>2232</v>
+      </c>
+      <c r="C49" s="64" t="s">
+        <v>2234</v>
+      </c>
+      <c r="D49" s="66" t="s">
         <v>2235</v>
       </c>
-      <c r="C49" s="64" t="s">
-        <v>2237</v>
-      </c>
-      <c r="D49" s="66" t="s">
-        <v>2238</v>
-      </c>
       <c r="E49" s="68" t="s">
-        <v>2239</v>
+        <v>2236</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>2236</v>
+        <v>2233</v>
       </c>
     </row>
   </sheetData>
@@ -18504,87 +18839,87 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CC04AFC-5339-4E19-966A-50FA9D7178EC}">
   <sheetPr codeName="Feuil1"/>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="16.85546875" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.5703125" style="138" customWidth="1"/>
     <col min="3" max="3" width="14.28515625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" style="5" customWidth="1"/>
     <col min="5" max="5" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24">
       <c r="A1" s="46" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="B1" s="134" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C1" s="38" t="s">
         <v>1859</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="D1" s="47" t="s">
         <v>1860</v>
       </c>
-      <c r="D1" s="47" t="s">
+      <c r="E1" s="38" t="s">
         <v>1861</v>
-      </c>
-      <c r="E1" s="38" t="s">
-        <v>1862</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="16" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="B2" s="10" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>1867</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="103" t="s">
         <v>1868</v>
       </c>
-      <c r="D2" s="103" t="s">
+      <c r="E2" s="9" t="s">
         <v>1869</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>1870</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="16" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="B3" s="10" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>1863</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="103" t="s">
         <v>1864</v>
       </c>
-      <c r="D3" s="103" t="s">
+      <c r="E3" s="9" t="s">
         <v>1865</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>1866</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="16" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>1870</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>1871</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="D4" s="103" t="s">
         <v>1872</v>
       </c>
-      <c r="D4" s="103" t="s">
+      <c r="E4" s="9" t="s">
         <v>1873</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>1874</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="24">
       <c r="A5" s="49" t="s">
-        <v>1955</v>
+        <v>1953</v>
       </c>
       <c r="B5" s="60" t="s">
         <v>843</v>
@@ -18733,7 +19068,7 @@
     </row>
     <row r="18" spans="1:5" ht="37.5">
       <c r="A18" s="50" t="s">
-        <v>1958</v>
+        <v>1956</v>
       </c>
       <c r="B18" s="134" t="s">
         <v>1693</v>
@@ -18745,1202 +19080,1410 @@
       <c r="E18" s="18"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="60" t="s">
-        <v>1801</v>
-      </c>
-      <c r="B19" s="137" t="s">
-        <v>1802</v>
-      </c>
-      <c r="C19" s="137" t="s">
-        <v>1951</v>
-      </c>
-      <c r="D19" s="107"/>
-      <c r="E19" s="18"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="11" t="s">
+      <c r="A19" s="11" t="s">
         <v>791</v>
       </c>
-      <c r="B20" s="135" t="s">
+      <c r="B19" s="135" t="s">
         <v>840</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C19" s="17" t="s">
         <v>946</v>
       </c>
-      <c r="D20" s="105" t="s">
+      <c r="D19" s="105" t="s">
         <v>1016</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E19" s="17" t="s">
         <v>1069</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
-        <v>2276</v>
-      </c>
-      <c r="B21" s="136" t="s">
-        <v>1658</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>1659</v>
-      </c>
-      <c r="D21" s="106" t="s">
-        <v>1660</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>1661</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="11" t="s">
-        <v>1614</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>1619</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>1620</v>
-      </c>
-      <c r="D22" s="103" t="s">
-        <v>217</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>217</v>
+    <row r="20" spans="1:5" ht="15">
+      <c r="A20" s="59" t="s">
+        <v>2966</v>
+      </c>
+      <c r="B20" s="59" t="s">
+        <v>2986</v>
+      </c>
+      <c r="C20" s="59" t="s">
+        <v>2987</v>
+      </c>
+      <c r="D20" s="59" t="s">
+        <v>2880</v>
+      </c>
+      <c r="E20" s="59" t="s">
+        <v>2880</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15">
+      <c r="A21" s="59" t="s">
+        <v>2964</v>
+      </c>
+      <c r="B21" s="59" t="s">
+        <v>2975</v>
+      </c>
+      <c r="C21" s="59" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D21" s="59" t="s">
+        <v>2977</v>
+      </c>
+      <c r="E21" s="59" t="s">
+        <v>2978</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="30">
+      <c r="A22" s="59" t="s">
+        <v>2979</v>
+      </c>
+      <c r="B22" s="59" t="s">
+        <v>2980</v>
+      </c>
+      <c r="C22" s="59" t="s">
+        <v>2981</v>
+      </c>
+      <c r="D22" s="59" t="s">
+        <v>2982</v>
+      </c>
+      <c r="E22" s="59" t="s">
+        <v>2983</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>1502</v>
-      </c>
-      <c r="B23" s="31" t="s">
-        <v>1501</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>1505</v>
-      </c>
-      <c r="D23" s="101" t="s">
-        <v>1503</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>1504</v>
+        <v>2273</v>
+      </c>
+      <c r="B23" s="136" t="s">
+        <v>1658</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D23" s="106" t="s">
+        <v>1660</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>1661</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="11" t="s">
-        <v>2474</v>
+        <v>1614</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>2475</v>
+        <v>1619</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>2476</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>2477</v>
+        <v>1620</v>
+      </c>
+      <c r="D24" s="103" t="s">
+        <v>217</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>2478</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="9" t="s">
-        <v>2669</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>2615</v>
-      </c>
-      <c r="C25" s="145" t="s">
-        <v>2616</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>2617</v>
-      </c>
-      <c r="E25" s="145" t="s">
-        <v>2618</v>
+      <c r="A25" s="6" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B25" s="31" t="s">
+        <v>1501</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D25" s="101" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>1504</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="11" t="s">
+        <v>2469</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>2470</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>2471</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>2472</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>2473</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="9" t="s">
+        <v>2664</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>2610</v>
+      </c>
+      <c r="C27" s="143" t="s">
+        <v>2611</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>2612</v>
+      </c>
+      <c r="E27" s="143" t="s">
+        <v>2613</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="11" t="s">
         <v>822</v>
       </c>
-      <c r="B26" s="135" t="s">
+      <c r="B28" s="135" t="s">
         <v>880</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C28" s="17" t="s">
         <v>903</v>
       </c>
-      <c r="D26" s="107"/>
-      <c r="E26" s="18"/>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="11" t="s">
-        <v>2040</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>2041</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>2042</v>
-      </c>
-      <c r="D27" s="103" t="s">
-        <v>217</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B28" s="136" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C28" s="17" t="s">
-        <v>1650</v>
-      </c>
-      <c r="D28" s="106" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>1649</v>
-      </c>
+      <c r="D28" s="107"/>
+      <c r="E28" s="18"/>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="11" t="s">
-        <v>564</v>
-      </c>
-      <c r="B29" s="135" t="s">
-        <v>754</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>755</v>
-      </c>
-      <c r="D29" s="105" t="s">
-        <v>1019</v>
-      </c>
-      <c r="E29" s="17" t="s">
-        <v>1020</v>
+        <v>2038</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>2039</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>2040</v>
+      </c>
+      <c r="D29" s="103" t="s">
+        <v>217</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="11" t="s">
-        <v>2035</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>2036</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>2037</v>
-      </c>
-      <c r="D30" s="103" t="s">
-        <v>2038</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>2039</v>
+      <c r="A30" s="6" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B30" s="136" t="s">
+        <v>1647</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D30" s="106" t="s">
+        <v>1648</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>1649</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="11" t="s">
-        <v>820</v>
+        <v>564</v>
       </c>
       <c r="B31" s="135" t="s">
-        <v>874</v>
+        <v>754</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>875</v>
+        <v>755</v>
       </c>
       <c r="D31" s="105" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="11" t="s">
-        <v>570</v>
-      </c>
-      <c r="B32" s="135" t="s">
-        <v>2313</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>919</v>
-      </c>
-      <c r="D32" s="105" t="s">
-        <v>1023</v>
-      </c>
-      <c r="E32" s="17" t="s">
-        <v>1024</v>
+        <v>2033</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>2034</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>2035</v>
+      </c>
+      <c r="D32" s="103" t="s">
+        <v>2036</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>2037</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="11" t="s">
+        <v>820</v>
+      </c>
+      <c r="B33" s="135" t="s">
+        <v>874</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>875</v>
+      </c>
+      <c r="D33" s="105" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="11" t="s">
+        <v>570</v>
+      </c>
+      <c r="B34" s="135" t="s">
+        <v>2310</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>919</v>
+      </c>
+      <c r="D34" s="105" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="11" t="s">
+        <v>2499</v>
+      </c>
+      <c r="B35" s="103" t="s">
+        <v>2500</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>2501</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>2502</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="37.5">
+      <c r="A36" s="11" t="s">
+        <v>825</v>
+      </c>
+      <c r="B36" s="135" t="s">
+        <v>884</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>885</v>
+      </c>
+      <c r="D36" s="105" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="37.5">
+      <c r="A37" s="11" t="s">
+        <v>882</v>
+      </c>
+      <c r="B37" s="135" t="s">
+        <v>883</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>896</v>
+      </c>
+      <c r="D37" s="107"/>
+      <c r="E37" s="18"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B38" s="31" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D38" s="101" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="11" t="s">
+        <v>2050</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>2051</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>2052</v>
+      </c>
+      <c r="D39" s="103" t="s">
+        <v>2053</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="11" t="s">
         <v>2504</v>
       </c>
-      <c r="B33" s="103" t="s">
+      <c r="B40" s="10" t="s">
         <v>2505</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C40" s="9" t="s">
         <v>2506</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D40" s="10" t="s">
         <v>2507</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E40" s="9" t="s">
         <v>2508</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="37.5">
-      <c r="A34" s="11" t="s">
-        <v>825</v>
-      </c>
-      <c r="B34" s="135" t="s">
-        <v>884</v>
-      </c>
-      <c r="C34" s="17" t="s">
-        <v>885</v>
-      </c>
-      <c r="D34" s="105" t="s">
-        <v>1025</v>
-      </c>
-      <c r="E34" s="17" t="s">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="37.5">
-      <c r="A35" s="11" t="s">
-        <v>882</v>
-      </c>
-      <c r="B35" s="135" t="s">
-        <v>883</v>
-      </c>
-      <c r="C35" s="17" t="s">
-        <v>896</v>
-      </c>
-      <c r="D35" s="107"/>
-      <c r="E35" s="18"/>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>1478</v>
-      </c>
-      <c r="B36" s="31" t="s">
-        <v>1491</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>1493</v>
-      </c>
-      <c r="D36" s="101" t="s">
-        <v>1492</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>1494</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="11" t="s">
-        <v>2053</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>2054</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>2055</v>
-      </c>
-      <c r="D37" s="103" t="s">
-        <v>2056</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>2057</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="11" t="s">
-        <v>2509</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>2510</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>2511</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>2512</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>2513</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>1438</v>
-      </c>
-      <c r="B39" s="31" t="s">
-        <v>1447</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>1448</v>
-      </c>
-      <c r="D39" s="101"/>
-      <c r="E39" s="1"/>
-    </row>
-    <row r="40" spans="1:5" ht="37.5">
-      <c r="A40" s="9" t="s">
-        <v>2836</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>2845</v>
-      </c>
-      <c r="C40" s="145" t="s">
-        <v>2846</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>2847</v>
-      </c>
-      <c r="E40" s="145" t="s">
-        <v>2848</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B41" s="31" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D41" s="101"/>
+      <c r="E41" s="1"/>
+    </row>
+    <row r="42" spans="1:5" ht="15">
+      <c r="A42" s="59" t="s">
+        <v>2973</v>
+      </c>
+      <c r="B42" s="59" t="s">
+        <v>3012</v>
+      </c>
+      <c r="C42" s="59" t="s">
+        <v>3014</v>
+      </c>
+      <c r="D42" s="59" t="s">
+        <v>3013</v>
+      </c>
+      <c r="E42" s="59" t="s">
+        <v>3015</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="80" t="s">
+        <v>2831</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>2840</v>
+      </c>
+      <c r="C43" s="143" t="s">
+        <v>2841</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>2842</v>
+      </c>
+      <c r="E43" s="143" t="s">
+        <v>2843</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="15">
+      <c r="A44" s="59" t="s">
+        <v>2967</v>
+      </c>
+      <c r="B44" s="59" t="s">
+        <v>2988</v>
+      </c>
+      <c r="C44" s="59" t="s">
+        <v>2989</v>
+      </c>
+      <c r="D44" s="59" t="s">
+        <v>2990</v>
+      </c>
+      <c r="E44" s="59" t="s">
+        <v>2991</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>1480</v>
       </c>
-      <c r="B41" s="31" t="s">
+      <c r="B45" s="31" t="s">
         <v>1497</v>
       </c>
-      <c r="C41" s="18" t="s">
+      <c r="C45" s="18" t="s">
         <v>1498</v>
       </c>
-      <c r="D41" s="101" t="s">
+      <c r="D45" s="101" t="s">
         <v>1499</v>
       </c>
-      <c r="E41" s="18" t="s">
+      <c r="E45" s="18" t="s">
         <v>1500</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="11" t="s">
-        <v>2032</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>2033</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>2034</v>
-      </c>
-      <c r="D42" s="103" t="s">
-        <v>217</v>
-      </c>
-      <c r="E42" s="9"/>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="11" t="s">
-        <v>855</v>
-      </c>
-      <c r="B43" s="135" t="s">
-        <v>856</v>
-      </c>
-      <c r="C43" s="17" t="s">
-        <v>857</v>
-      </c>
-      <c r="D43" s="106" t="s">
-        <v>1061</v>
-      </c>
-      <c r="E43" s="18" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="11" t="s">
-        <v>876</v>
-      </c>
-      <c r="B44" s="135" t="s">
-        <v>877</v>
-      </c>
-      <c r="C44" s="17" t="s">
-        <v>878</v>
-      </c>
-      <c r="D44" s="106" t="s">
-        <v>1063</v>
-      </c>
-      <c r="E44" s="18" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="11" t="s">
-        <v>1242</v>
-      </c>
-      <c r="B45" s="136" t="s">
-        <v>1245</v>
-      </c>
-      <c r="C45" s="17" t="s">
-        <v>1243</v>
-      </c>
-      <c r="D45" s="106" t="s">
-        <v>1246</v>
-      </c>
-      <c r="E45" s="18" t="s">
-        <v>1244</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="11" t="s">
-        <v>897</v>
-      </c>
-      <c r="B46" s="135" t="s">
-        <v>898</v>
-      </c>
-      <c r="C46" s="17" t="s">
-        <v>899</v>
-      </c>
-      <c r="D46" s="107"/>
-      <c r="E46" s="18"/>
+        <v>2030</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>2031</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>2032</v>
+      </c>
+      <c r="D46" s="103" t="s">
+        <v>217</v>
+      </c>
+      <c r="E46" s="9"/>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="11" t="s">
-        <v>2182</v>
-      </c>
-      <c r="B47" s="10" t="s">
-        <v>2183</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>2184</v>
-      </c>
-      <c r="D47" s="103" t="s">
-        <v>2185</v>
-      </c>
-      <c r="E47" s="9" t="s">
-        <v>2186</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="19" t="s">
-        <v>1172</v>
-      </c>
-      <c r="B48" s="135" t="s">
-        <v>1192</v>
-      </c>
-      <c r="C48" s="17" t="s">
-        <v>1193</v>
-      </c>
-      <c r="D48" s="105" t="s">
-        <v>1194</v>
-      </c>
-      <c r="E48" s="17" t="s">
-        <v>1195</v>
+        <v>855</v>
+      </c>
+      <c r="B47" s="135" t="s">
+        <v>856</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>857</v>
+      </c>
+      <c r="D47" s="106" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E47" s="18" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="15">
+      <c r="A48" s="59" t="s">
+        <v>2971</v>
+      </c>
+      <c r="B48" s="59" t="s">
+        <v>3004</v>
+      </c>
+      <c r="C48" s="59" t="s">
+        <v>3005</v>
+      </c>
+      <c r="D48" s="59" t="s">
+        <v>3006</v>
+      </c>
+      <c r="E48" s="59" t="s">
+        <v>3007</v>
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="19" t="s">
-        <v>1641</v>
-      </c>
-      <c r="B49" s="136" t="s">
-        <v>1651</v>
+      <c r="A49" s="11" t="s">
+        <v>876</v>
+      </c>
+      <c r="B49" s="135" t="s">
+        <v>877</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>1652</v>
+        <v>878</v>
       </c>
       <c r="D49" s="106" t="s">
-        <v>1653</v>
-      </c>
-      <c r="E49" s="17" t="s">
-        <v>217</v>
+        <v>1063</v>
+      </c>
+      <c r="E49" s="18" t="s">
+        <v>1064</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="11" t="s">
-        <v>2201</v>
-      </c>
-      <c r="B50" s="10" t="s">
-        <v>2202</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>2203</v>
-      </c>
-      <c r="D50" s="103" t="s">
-        <v>2204</v>
-      </c>
-      <c r="E50" s="9" t="s">
-        <v>2205</v>
+        <v>1242</v>
+      </c>
+      <c r="B50" s="136" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C50" s="17" t="s">
+        <v>1243</v>
+      </c>
+      <c r="D50" s="106" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E50" s="18" t="s">
+        <v>1244</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="11" t="s">
-        <v>1612</v>
-      </c>
-      <c r="B51" s="10" t="s">
-        <v>1615</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>1616</v>
-      </c>
-      <c r="D51" s="103" t="s">
+        <v>897</v>
+      </c>
+      <c r="B51" s="135" t="s">
+        <v>898</v>
+      </c>
+      <c r="C51" s="17" t="s">
+        <v>899</v>
+      </c>
+      <c r="D51" s="107"/>
+      <c r="E51" s="18"/>
+    </row>
+    <row r="52" spans="1:5" ht="15">
+      <c r="A52" s="59" t="s">
+        <v>2970</v>
+      </c>
+      <c r="B52" s="59" t="s">
+        <v>1801</v>
+      </c>
+      <c r="C52" s="59" t="s">
+        <v>3016</v>
+      </c>
+      <c r="D52" s="59" t="s">
+        <v>3003</v>
+      </c>
+      <c r="E52" s="59" t="s">
+        <v>3017</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="11" t="s">
+        <v>2179</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>2180</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D53" s="103" t="s">
+        <v>2182</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="19" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B54" s="135" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C54" s="17" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D54" s="105" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E54" s="17" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="19" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B55" s="136" t="s">
+        <v>1651</v>
+      </c>
+      <c r="C55" s="17" t="s">
+        <v>1652</v>
+      </c>
+      <c r="D55" s="106" t="s">
+        <v>1653</v>
+      </c>
+      <c r="E55" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="E51" s="9" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>940</v>
-      </c>
-      <c r="B52" s="137" t="s">
-        <v>941</v>
-      </c>
-      <c r="C52" s="18" t="s">
-        <v>942</v>
-      </c>
-      <c r="D52" s="105" t="s">
-        <v>1037</v>
-      </c>
-      <c r="E52" s="17" t="s">
-        <v>1078</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>912</v>
-      </c>
-      <c r="B53" s="136" t="s">
-        <v>943</v>
-      </c>
-      <c r="C53" s="18" t="s">
-        <v>915</v>
-      </c>
-      <c r="D53" s="105" t="s">
-        <v>1038</v>
-      </c>
-      <c r="E53" s="17" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="37.5">
-      <c r="A54" s="11" t="s">
-        <v>2206</v>
-      </c>
-      <c r="B54" s="10" t="s">
-        <v>2207</v>
-      </c>
-      <c r="C54" s="9" t="s">
-        <v>2208</v>
-      </c>
-      <c r="D54" s="103" t="s">
-        <v>2209</v>
-      </c>
-      <c r="E54" s="9" t="s">
-        <v>2210</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="9" t="s">
-        <v>2837</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>2849</v>
-      </c>
-      <c r="C55" s="145" t="s">
-        <v>2850</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>2851</v>
-      </c>
-      <c r="E55" s="145" t="s">
-        <v>2852</v>
-      </c>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>913</v>
-      </c>
-      <c r="B56" s="136" t="s">
-        <v>944</v>
-      </c>
-      <c r="C56" s="18" t="s">
-        <v>914</v>
-      </c>
-      <c r="D56" s="105" t="s">
-        <v>1040</v>
-      </c>
-      <c r="E56" s="17" t="s">
-        <v>1041</v>
+      <c r="A56" s="11" t="s">
+        <v>2198</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>2199</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>2200</v>
+      </c>
+      <c r="D56" s="103" t="s">
+        <v>2201</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>2202</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="11" t="s">
-        <v>756</v>
-      </c>
-      <c r="B57" s="135" t="s">
-        <v>757</v>
-      </c>
-      <c r="C57" s="17" t="s">
-        <v>758</v>
-      </c>
-      <c r="D57" s="105" t="s">
-        <v>1042</v>
-      </c>
-      <c r="E57" s="17" t="s">
-        <v>1043</v>
+        <v>1612</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>1615</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>1616</v>
+      </c>
+      <c r="D57" s="103" t="s">
+        <v>217</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>1436</v>
-      </c>
-      <c r="B58" s="31" t="s">
-        <v>1439</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>1440</v>
-      </c>
-      <c r="D58" s="101" t="s">
-        <v>1441</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>1442</v>
+        <v>940</v>
+      </c>
+      <c r="B58" s="137" t="s">
+        <v>941</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>942</v>
+      </c>
+      <c r="D58" s="105" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E58" s="17" t="s">
+        <v>1078</v>
       </c>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="11" t="s">
-        <v>2216</v>
-      </c>
-      <c r="B59" s="10" t="s">
-        <v>2217</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>2218</v>
-      </c>
-      <c r="D59" s="103" t="s">
-        <v>2219</v>
-      </c>
-      <c r="E59" s="9" t="s">
-        <v>2220</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="B59" s="136" t="s">
+        <v>943</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>915</v>
+      </c>
+      <c r="D59" s="105" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E59" s="17" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="37.5">
       <c r="A60" s="11" t="s">
-        <v>2499</v>
+        <v>2203</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>2500</v>
+        <v>2204</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>2501</v>
-      </c>
-      <c r="D60" s="10" t="s">
-        <v>2502</v>
+        <v>2205</v>
+      </c>
+      <c r="D60" s="103" t="s">
+        <v>2206</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>2503</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="37.5">
+        <v>2207</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
       <c r="A61" s="9" t="s">
-        <v>2840</v>
+        <v>2832</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>2841</v>
-      </c>
-      <c r="C61" s="145" t="s">
-        <v>2842</v>
+        <v>2844</v>
+      </c>
+      <c r="C61" s="143" t="s">
+        <v>2845</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>2843</v>
-      </c>
-      <c r="E61" s="145" t="s">
-        <v>2844</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="37.5">
-      <c r="A62" s="11" t="s">
-        <v>2122</v>
-      </c>
-      <c r="B62" s="10" t="s">
-        <v>2123</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>2124</v>
-      </c>
-      <c r="D62" s="103" t="s">
-        <v>2125</v>
-      </c>
-      <c r="E62" s="9" t="s">
-        <v>2126</v>
+        <v>2846</v>
+      </c>
+      <c r="E61" s="143" t="s">
+        <v>2847</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>913</v>
+      </c>
+      <c r="B62" s="136" t="s">
+        <v>944</v>
+      </c>
+      <c r="C62" s="18" t="s">
+        <v>914</v>
+      </c>
+      <c r="D62" s="105" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E62" s="17" t="s">
+        <v>1041</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="11" t="s">
-        <v>2028</v>
-      </c>
-      <c r="B63" s="10" t="s">
-        <v>2029</v>
-      </c>
-      <c r="C63" s="9" t="s">
-        <v>2030</v>
-      </c>
-      <c r="D63" s="103" t="s">
-        <v>1304</v>
-      </c>
-      <c r="E63" s="9" t="s">
-        <v>2031</v>
+        <v>756</v>
+      </c>
+      <c r="B63" s="135" t="s">
+        <v>757</v>
+      </c>
+      <c r="C63" s="17" t="s">
+        <v>758</v>
+      </c>
+      <c r="D63" s="105" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E63" s="17" t="s">
+        <v>1043</v>
       </c>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="11" t="s">
-        <v>2043</v>
-      </c>
-      <c r="B64" s="10" t="s">
-        <v>2044</v>
-      </c>
-      <c r="C64" s="9" t="s">
-        <v>2045</v>
-      </c>
-      <c r="D64" s="103" t="s">
-        <v>217</v>
-      </c>
-      <c r="E64" s="9" t="s">
-        <v>217</v>
+      <c r="A64" s="6" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B64" s="31" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>1440</v>
+      </c>
+      <c r="D64" s="101" t="s">
+        <v>1441</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>1442</v>
       </c>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="38" t="s">
-        <v>2372</v>
-      </c>
-      <c r="B65" s="47" t="s">
-        <v>2385</v>
-      </c>
-      <c r="C65" s="38" t="s">
-        <v>2384</v>
-      </c>
-      <c r="D65" s="47" t="s">
-        <v>2386</v>
-      </c>
-      <c r="E65" s="38" t="s">
-        <v>2387</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="11" t="s">
-        <v>571</v>
-      </c>
-      <c r="B66" s="135" t="s">
-        <v>759</v>
-      </c>
-      <c r="C66" s="17" t="s">
-        <v>816</v>
-      </c>
-      <c r="D66" s="105" t="s">
-        <v>1044</v>
-      </c>
-      <c r="E66" s="17" t="s">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="19" t="s">
-        <v>1169</v>
-      </c>
-      <c r="B67" s="135" t="s">
-        <v>1186</v>
-      </c>
-      <c r="C67" s="17" t="s">
-        <v>1187</v>
-      </c>
-      <c r="D67" s="105" t="s">
-        <v>217</v>
-      </c>
-      <c r="E67" s="17" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="24" customHeight="1">
+      <c r="A65" s="11" t="s">
+        <v>2213</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>2214</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>2215</v>
+      </c>
+      <c r="D65" s="103" t="s">
+        <v>2216</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>2217</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="15">
+      <c r="A66" s="59" t="s">
+        <v>2213</v>
+      </c>
+      <c r="B66" s="59" t="s">
+        <v>2214</v>
+      </c>
+      <c r="C66" s="59" t="s">
+        <v>2215</v>
+      </c>
+      <c r="D66" s="59" t="s">
+        <v>2216</v>
+      </c>
+      <c r="E66" s="59" t="s">
+        <v>2217</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="24" customHeight="1">
+      <c r="A67" s="59" t="s">
+        <v>2996</v>
+      </c>
+      <c r="B67" s="59" t="s">
+        <v>2997</v>
+      </c>
+      <c r="C67" s="59" t="s">
+        <v>2998</v>
+      </c>
+      <c r="D67" s="59" t="s">
+        <v>2999</v>
+      </c>
+      <c r="E67" s="59" t="s">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
       <c r="A68" s="11" t="s">
-        <v>821</v>
-      </c>
-      <c r="B68" s="135" t="s">
-        <v>879</v>
-      </c>
-      <c r="C68" s="17" t="s">
-        <v>895</v>
-      </c>
-      <c r="D68" s="107"/>
-      <c r="E68" s="18"/>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="19" t="s">
-        <v>1642</v>
-      </c>
-      <c r="B69" s="136" t="s">
-        <v>1654</v>
-      </c>
-      <c r="C69" s="17" t="s">
-        <v>1655</v>
-      </c>
-      <c r="D69" s="106" t="s">
-        <v>1656</v>
-      </c>
-      <c r="E69" s="17" t="s">
-        <v>1657</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
+        <v>2494</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>2495</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>2496</v>
+      </c>
+      <c r="D68" s="10" t="s">
+        <v>2497</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="37.5">
+      <c r="A69" s="9" t="s">
+        <v>2835</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>2836</v>
+      </c>
+      <c r="C69" s="143" t="s">
+        <v>2837</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>2838</v>
+      </c>
+      <c r="E69" s="143" t="s">
+        <v>2839</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="37.5">
       <c r="A70" s="11" t="s">
-        <v>490</v>
-      </c>
-      <c r="B70" s="135" t="s">
-        <v>520</v>
-      </c>
-      <c r="C70" s="17" t="s">
-        <v>521</v>
-      </c>
-      <c r="D70" s="105" t="s">
-        <v>1046</v>
-      </c>
-      <c r="E70" s="17" t="s">
-        <v>1047</v>
+        <v>2119</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>2120</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>2121</v>
+      </c>
+      <c r="D70" s="103" t="s">
+        <v>2122</v>
+      </c>
+      <c r="E70" s="9" t="s">
+        <v>2123</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="11" t="s">
-        <v>904</v>
-      </c>
-      <c r="B71" s="135" t="s">
-        <v>906</v>
-      </c>
-      <c r="C71" s="17" t="s">
-        <v>905</v>
-      </c>
-      <c r="D71" s="105" t="s">
-        <v>1048</v>
-      </c>
-      <c r="E71" s="17" t="s">
-        <v>1049</v>
+        <v>2026</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>2027</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>2028</v>
+      </c>
+      <c r="D71" s="103" t="s">
+        <v>1304</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>2029</v>
       </c>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="19" t="s">
-        <v>1709</v>
-      </c>
-      <c r="B72" s="136" t="s">
-        <v>1710</v>
-      </c>
-      <c r="C72" s="17" t="s">
-        <v>1712</v>
-      </c>
-      <c r="D72" s="106" t="s">
-        <v>1711</v>
-      </c>
-      <c r="E72" s="17" t="s">
-        <v>1713</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="11" t="s">
-        <v>2151</v>
-      </c>
-      <c r="B73" s="10" t="s">
-        <v>2152</v>
-      </c>
-      <c r="C73" s="9" t="s">
-        <v>2153</v>
-      </c>
-      <c r="D73" s="103" t="s">
-        <v>2154</v>
-      </c>
-      <c r="E73" s="9" t="s">
-        <v>2155</v>
+      <c r="A72" s="11" t="s">
+        <v>2041</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>2042</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>2043</v>
+      </c>
+      <c r="D72" s="103" t="s">
+        <v>217</v>
+      </c>
+      <c r="E72" s="9" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="15">
+      <c r="A73" s="59" t="s">
+        <v>2965</v>
+      </c>
+      <c r="B73" s="59" t="s">
+        <v>2984</v>
+      </c>
+      <c r="C73" s="59" t="s">
+        <v>2985</v>
+      </c>
+      <c r="D73" s="59" t="s">
+        <v>2880</v>
+      </c>
+      <c r="E73" s="59" t="s">
+        <v>2880</v>
       </c>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="11" t="s">
-        <v>2051</v>
-      </c>
-      <c r="B74" s="10" t="s">
-        <v>2052</v>
-      </c>
-      <c r="C74" s="9" t="s">
-        <v>2051</v>
-      </c>
-      <c r="D74" s="103" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E74" s="9" t="s">
-        <v>2059</v>
+      <c r="A74" s="38" t="s">
+        <v>2369</v>
+      </c>
+      <c r="B74" s="47" t="s">
+        <v>2382</v>
+      </c>
+      <c r="C74" s="38" t="s">
+        <v>2381</v>
+      </c>
+      <c r="D74" s="47" t="s">
+        <v>2383</v>
+      </c>
+      <c r="E74" s="38" t="s">
+        <v>2384</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="11" t="s">
-        <v>819</v>
+        <v>571</v>
       </c>
       <c r="B75" s="135" t="s">
-        <v>873</v>
+        <v>759</v>
       </c>
       <c r="C75" s="17" t="s">
-        <v>890</v>
+        <v>816</v>
       </c>
       <c r="D75" s="105" t="s">
-        <v>1033</v>
+        <v>1044</v>
       </c>
       <c r="E75" s="17" t="s">
-        <v>1079</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="76" spans="1:5">
-      <c r="A76" s="11" t="s">
-        <v>781</v>
+      <c r="A76" s="19" t="s">
+        <v>1169</v>
       </c>
       <c r="B76" s="135" t="s">
-        <v>827</v>
+        <v>1186</v>
       </c>
       <c r="C76" s="17" t="s">
-        <v>828</v>
-      </c>
-      <c r="D76" s="107"/>
-      <c r="E76" s="18"/>
+        <v>1187</v>
+      </c>
+      <c r="D76" s="105" t="s">
+        <v>217</v>
+      </c>
+      <c r="E76" s="17" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="77" spans="1:5">
-      <c r="A77" s="19" t="s">
-        <v>1467</v>
-      </c>
-      <c r="B77" s="31" t="s">
-        <v>1468</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>1469</v>
-      </c>
-      <c r="D77" s="101" t="s">
-        <v>1470</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>1471</v>
-      </c>
+      <c r="A77" s="11" t="s">
+        <v>821</v>
+      </c>
+      <c r="B77" s="135" t="s">
+        <v>879</v>
+      </c>
+      <c r="C77" s="17" t="s">
+        <v>895</v>
+      </c>
+      <c r="D77" s="107"/>
+      <c r="E77" s="18"/>
     </row>
     <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>1437</v>
-      </c>
-      <c r="B78" s="31" t="s">
-        <v>1443</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>1444</v>
-      </c>
-      <c r="D78" s="101" t="s">
-        <v>1445</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>1446</v>
+      <c r="A78" s="19" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B78" s="136" t="s">
+        <v>1654</v>
+      </c>
+      <c r="C78" s="17" t="s">
+        <v>1655</v>
+      </c>
+      <c r="D78" s="106" t="s">
+        <v>1656</v>
+      </c>
+      <c r="E78" s="17" t="s">
+        <v>1657</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="11" t="s">
-        <v>1477</v>
-      </c>
-      <c r="B79" s="31" t="s">
-        <v>1487</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>1488</v>
-      </c>
-      <c r="D79" s="101" t="s">
-        <v>1489</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>1490</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" ht="37.5">
+        <v>490</v>
+      </c>
+      <c r="B79" s="135" t="s">
+        <v>520</v>
+      </c>
+      <c r="C79" s="17" t="s">
+        <v>521</v>
+      </c>
+      <c r="D79" s="105" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E79" s="17" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
       <c r="A80" s="11" t="s">
-        <v>2146</v>
-      </c>
-      <c r="B80" s="10" t="s">
-        <v>2147</v>
-      </c>
-      <c r="C80" s="9" t="s">
-        <v>2148</v>
-      </c>
-      <c r="D80" s="103" t="s">
-        <v>2149</v>
-      </c>
-      <c r="E80" s="9" t="s">
-        <v>2150</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="11" t="s">
-        <v>817</v>
-      </c>
-      <c r="B81" s="135" t="s">
-        <v>870</v>
-      </c>
-      <c r="C81" s="17" t="s">
-        <v>894</v>
-      </c>
-      <c r="D81" s="105" t="s">
-        <v>1034</v>
-      </c>
-      <c r="E81" s="17" t="s">
-        <v>1080</v>
+        <v>904</v>
+      </c>
+      <c r="B80" s="135" t="s">
+        <v>906</v>
+      </c>
+      <c r="C80" s="17" t="s">
+        <v>905</v>
+      </c>
+      <c r="D80" s="105" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E80" s="17" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="15">
+      <c r="A81" s="59" t="s">
+        <v>2969</v>
+      </c>
+      <c r="B81" s="59" t="s">
+        <v>3001</v>
+      </c>
+      <c r="C81" s="59" t="s">
+        <v>3002</v>
+      </c>
+      <c r="D81" s="59" t="s">
+        <v>2880</v>
+      </c>
+      <c r="E81" s="59" t="s">
+        <v>2880</v>
       </c>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="11" t="s">
-        <v>2115</v>
-      </c>
-      <c r="B82" s="10" t="s">
-        <v>2116</v>
-      </c>
-      <c r="C82" s="9" t="s">
-        <v>2117</v>
-      </c>
-      <c r="D82" s="103" t="s">
-        <v>2118</v>
-      </c>
-      <c r="E82" s="9" t="s">
-        <v>2119</v>
+      <c r="A82" s="19" t="s">
+        <v>1709</v>
+      </c>
+      <c r="B82" s="136" t="s">
+        <v>1710</v>
+      </c>
+      <c r="C82" s="17" t="s">
+        <v>1712</v>
+      </c>
+      <c r="D82" s="106" t="s">
+        <v>1711</v>
+      </c>
+      <c r="E82" s="17" t="s">
+        <v>1713</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="11" t="s">
-        <v>2060</v>
+        <v>2148</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>2061</v>
+        <v>2149</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>2062</v>
+        <v>2150</v>
       </c>
       <c r="D83" s="103" t="s">
-        <v>2063</v>
+        <v>2151</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>2064</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="11" t="s">
-        <v>2290</v>
+        <v>2048</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>2291</v>
+        <v>2049</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>2292</v>
+        <v>2048</v>
       </c>
       <c r="D84" s="103" t="s">
-        <v>2294</v>
+        <v>2055</v>
       </c>
       <c r="E84" s="9" t="s">
-        <v>2293</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="11" t="s">
-        <v>2157</v>
-      </c>
-      <c r="B85" s="10" t="s">
-        <v>2158</v>
-      </c>
-      <c r="C85" s="9" t="s">
-        <v>2159</v>
-      </c>
-      <c r="D85" s="103" t="s">
-        <v>1025</v>
-      </c>
-      <c r="E85" s="9" t="s">
-        <v>1026</v>
+        <v>819</v>
+      </c>
+      <c r="B85" s="135" t="s">
+        <v>873</v>
+      </c>
+      <c r="C85" s="17" t="s">
+        <v>890</v>
+      </c>
+      <c r="D85" s="105" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E85" s="17" t="s">
+        <v>1079</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="11" t="s">
-        <v>578</v>
+        <v>781</v>
       </c>
       <c r="B86" s="135" t="s">
-        <v>765</v>
+        <v>827</v>
       </c>
       <c r="C86" s="17" t="s">
-        <v>766</v>
-      </c>
-      <c r="D86" s="105" t="s">
-        <v>1056</v>
-      </c>
-      <c r="E86" s="17" t="s">
-        <v>1057</v>
-      </c>
+        <v>828</v>
+      </c>
+      <c r="D86" s="107"/>
+      <c r="E86" s="18"/>
     </row>
     <row r="87" spans="1:5">
-      <c r="A87" s="11" t="s">
-        <v>2187</v>
-      </c>
-      <c r="B87" s="10" t="s">
-        <v>2188</v>
-      </c>
-      <c r="C87" s="9" t="s">
-        <v>2189</v>
-      </c>
-      <c r="D87" s="103" t="s">
-        <v>2190</v>
-      </c>
-      <c r="E87" s="9" t="s">
-        <v>2191</v>
+      <c r="A87" s="19" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B87" s="31" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>1469</v>
+      </c>
+      <c r="D87" s="101" t="s">
+        <v>1470</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>1471</v>
       </c>
     </row>
     <row r="88" spans="1:5">
-      <c r="A88" s="19" t="s">
-        <v>1248</v>
-      </c>
-      <c r="B88" s="136" t="s">
-        <v>1249</v>
-      </c>
-      <c r="C88" s="17" t="s">
-        <v>1251</v>
-      </c>
-      <c r="D88" s="106" t="s">
-        <v>1250</v>
-      </c>
-      <c r="E88" s="17" t="s">
-        <v>1252</v>
+      <c r="A88" s="6" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B88" s="31" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>1444</v>
+      </c>
+      <c r="D88" s="101" t="s">
+        <v>1445</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>1446</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="11" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B89" s="31" t="s">
+        <v>1487</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D89" s="101" t="s">
+        <v>1489</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="37.5">
+      <c r="A90" s="11" t="s">
+        <v>2143</v>
+      </c>
+      <c r="B90" s="10" t="s">
+        <v>2144</v>
+      </c>
+      <c r="C90" s="9" t="s">
+        <v>2145</v>
+      </c>
+      <c r="D90" s="103" t="s">
+        <v>2146</v>
+      </c>
+      <c r="E90" s="9" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="11" t="s">
+        <v>817</v>
+      </c>
+      <c r="B91" s="135" t="s">
+        <v>870</v>
+      </c>
+      <c r="C91" s="17" t="s">
+        <v>894</v>
+      </c>
+      <c r="D91" s="105" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E91" s="17" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="11" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B92" s="10" t="s">
+        <v>2113</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>2114</v>
+      </c>
+      <c r="D92" s="103" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E92" s="9" t="s">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="11" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B93" s="10" t="s">
+        <v>2058</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>2059</v>
+      </c>
+      <c r="D93" s="103" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E93" s="9" t="s">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="11" t="s">
+        <v>2287</v>
+      </c>
+      <c r="B94" s="10" t="s">
+        <v>2288</v>
+      </c>
+      <c r="C94" s="9" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D94" s="103" t="s">
+        <v>2291</v>
+      </c>
+      <c r="E94" s="9" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="11" t="s">
+        <v>2154</v>
+      </c>
+      <c r="B95" s="10" t="s">
+        <v>2155</v>
+      </c>
+      <c r="C95" s="9" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D95" s="103" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E95" s="9" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="15">
+      <c r="A96" s="59" t="s">
+        <v>2972</v>
+      </c>
+      <c r="B96" s="59" t="s">
+        <v>3008</v>
+      </c>
+      <c r="C96" s="59" t="s">
+        <v>3009</v>
+      </c>
+      <c r="D96" s="59" t="s">
+        <v>3010</v>
+      </c>
+      <c r="E96" s="59" t="s">
+        <v>3011</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="11" t="s">
+        <v>578</v>
+      </c>
+      <c r="B97" s="135" t="s">
+        <v>765</v>
+      </c>
+      <c r="C97" s="17" t="s">
+        <v>766</v>
+      </c>
+      <c r="D97" s="105" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E97" s="17" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="11" t="s">
+        <v>2184</v>
+      </c>
+      <c r="B98" s="10" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C98" s="9" t="s">
+        <v>2186</v>
+      </c>
+      <c r="D98" s="103" t="s">
+        <v>2187</v>
+      </c>
+      <c r="E98" s="9" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="19" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B99" s="136" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C99" s="17" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D99" s="106" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E99" s="17" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="15">
+      <c r="A100" s="59" t="s">
+        <v>2968</v>
+      </c>
+      <c r="B100" s="59" t="s">
+        <v>2992</v>
+      </c>
+      <c r="C100" s="59" t="s">
+        <v>2993</v>
+      </c>
+      <c r="D100" s="59" t="s">
+        <v>2994</v>
+      </c>
+      <c r="E100" s="59" t="s">
+        <v>2995</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="11" t="s">
+        <v>2974</v>
+      </c>
+      <c r="B101" s="10" t="s">
+        <v>2044</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>2045</v>
+      </c>
+      <c r="D101" s="103" t="s">
         <v>2046</v>
       </c>
-      <c r="B89" s="10" t="s">
+      <c r="E101" s="9" t="s">
         <v>2047</v>
       </c>
-      <c r="C89" s="9" t="s">
-        <v>2048</v>
-      </c>
-      <c r="D89" s="103" t="s">
-        <v>2049</v>
-      </c>
-      <c r="E89" s="9" t="s">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" s="9" t="s">
-        <v>2120</v>
-      </c>
-      <c r="B90" s="9" t="s">
-        <v>2121</v>
-      </c>
-      <c r="C90" s="145" t="s">
-        <v>2120</v>
-      </c>
-      <c r="D90" s="9" t="s">
-        <v>2838</v>
-      </c>
-      <c r="E90" s="145" t="s">
-        <v>2839</v>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="9" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B102" s="9" t="s">
+        <v>2118</v>
+      </c>
+      <c r="C102" s="143" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D102" s="9" t="s">
+        <v>2833</v>
+      </c>
+      <c r="E102" s="143" t="s">
+        <v>2834</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A19:E90">
-    <sortCondition ref="A19:A90"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A20:E102">
+    <sortCondition ref="A19:A102"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -19961,7 +20504,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75">
       <c r="A1" s="38" t="s">
-        <v>1957</v>
+        <v>1955</v>
       </c>
       <c r="B1" s="134" t="s">
         <v>1578</v>
@@ -19978,19 +20521,19 @@
     </row>
     <row r="2" spans="1:5" ht="18.75">
       <c r="A2" s="11" t="s">
-        <v>2518</v>
+        <v>2513</v>
       </c>
       <c r="B2" s="103" t="s">
         <v>1580</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>2520</v>
+        <v>2515</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>1581</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>2527</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="27.75" customHeight="1">
@@ -20018,47 +20561,47 @@
         <v>544</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>2547</v>
+        <v>2542</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>1027</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>2548</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18.75">
       <c r="A5" s="11" t="s">
-        <v>2514</v>
+        <v>2509</v>
       </c>
       <c r="B5" s="103" t="s">
-        <v>2516</v>
+        <v>2511</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>2515</v>
+        <v>2510</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>2525</v>
+        <v>2520</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>2526</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18.75" customHeight="1">
       <c r="A6" s="11" t="s">
-        <v>2549</v>
+        <v>2544</v>
       </c>
       <c r="B6" s="103" t="s">
-        <v>2550</v>
+        <v>2545</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>2551</v>
+        <v>2546</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>2552</v>
+        <v>2547</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>2553</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18.75" customHeight="1">
@@ -20080,19 +20623,19 @@
     </row>
     <row r="8" spans="1:5" ht="18.75" customHeight="1">
       <c r="A8" s="11" t="s">
-        <v>2522</v>
+        <v>2517</v>
       </c>
       <c r="B8" s="103" t="s">
-        <v>2540</v>
+        <v>2535</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>2541</v>
+        <v>2536</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>2542</v>
+        <v>2537</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>2543</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18.75" customHeight="1">
@@ -20103,64 +20646,64 @@
         <v>841</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>2524</v>
+        <v>2519</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>841</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>2524</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18.75" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>2521</v>
+        <v>2516</v>
       </c>
       <c r="B10" s="103" t="s">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>2537</v>
+        <v>2532</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>2538</v>
+        <v>2533</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>2539</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18.75" customHeight="1">
       <c r="A11" s="11" t="s">
-        <v>2519</v>
+        <v>2514</v>
       </c>
       <c r="B11" s="103" t="s">
-        <v>2528</v>
+        <v>2523</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>2529</v>
+        <v>2524</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>2530</v>
+        <v>2525</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>2531</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="37.5">
       <c r="A12" s="11" t="s">
-        <v>2523</v>
+        <v>2518</v>
       </c>
       <c r="B12" s="103" t="s">
-        <v>2544</v>
+        <v>2539</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>2545</v>
+        <v>2540</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>2544</v>
+        <v>2539</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>2545</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18.75">
@@ -20171,7 +20714,7 @@
         <v>839</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>2546</v>
+        <v>2541</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>1050</v>
@@ -20182,19 +20725,19 @@
     </row>
     <row r="14" spans="1:5" ht="18.75">
       <c r="A14" s="11" t="s">
-        <v>2517</v>
+        <v>2512</v>
       </c>
       <c r="B14" s="103" t="s">
-        <v>2532</v>
+        <v>2527</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>2533</v>
+        <v>2528</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>2534</v>
+        <v>2529</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>2535</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18.75">
@@ -20239,7 +20782,7 @@
         <v>1756</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>2624</v>
+        <v>2619</v>
       </c>
       <c r="D17" s="101"/>
       <c r="E17" s="1"/>
@@ -20280,7 +20823,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75">
       <c r="A1" s="47" t="s">
-        <v>1956</v>
+        <v>1954</v>
       </c>
       <c r="B1" s="47" t="s">
         <v>1697</v>
@@ -20427,7 +20970,7 @@
         <v>826</v>
       </c>
       <c r="B10" s="105" t="s">
-        <v>2314</v>
+        <v>2311</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>902</v>
@@ -20622,83 +21165,83 @@
     </row>
     <row r="2" spans="1:5" ht="21" customHeight="1">
       <c r="A2" s="6" t="s">
+        <v>2350</v>
+      </c>
+      <c r="B2" s="107" t="s">
+        <v>2351</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>2352</v>
+      </c>
+      <c r="D2" s="105" t="s">
         <v>2353</v>
       </c>
-      <c r="B2" s="107" t="s">
+      <c r="E2" s="17" t="s">
         <v>2354</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>2355</v>
-      </c>
-      <c r="D2" s="105" t="s">
-        <v>2356</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>2357</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="21" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>2576</v>
+        <v>2571</v>
       </c>
       <c r="B3" s="107" t="s">
-        <v>2104</v>
+        <v>2101</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>2577</v>
+        <v>2572</v>
       </c>
       <c r="D3" s="105" t="s">
-        <v>2106</v>
+        <v>2103</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>2578</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="21" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>2573</v>
+        <v>2568</v>
       </c>
       <c r="B4" s="107" t="s">
-        <v>2574</v>
+        <v>2569</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>2575</v>
+        <v>2570</v>
       </c>
       <c r="D4" s="105"/>
       <c r="E4" s="17"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="11" t="s">
+        <v>2275</v>
+      </c>
+      <c r="B5" s="105" t="s">
+        <v>2276</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>2277</v>
+      </c>
+      <c r="D5" s="105" t="s">
         <v>2278</v>
       </c>
-      <c r="B5" s="105" t="s">
+      <c r="E5" s="17" t="s">
         <v>2279</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>2280</v>
-      </c>
-      <c r="D5" s="105" t="s">
-        <v>2281</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>2282</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="37.5">
       <c r="A6" s="11" t="s">
+        <v>2364</v>
+      </c>
+      <c r="B6" s="105" t="s">
+        <v>2365</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>2366</v>
+      </c>
+      <c r="D6" s="105" t="s">
         <v>2367</v>
       </c>
-      <c r="B6" s="105" t="s">
+      <c r="E6" s="17" t="s">
         <v>2368</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>2369</v>
-      </c>
-      <c r="D6" s="105" t="s">
-        <v>2370</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>2371</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -20715,12 +21258,12 @@
         <v>968</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>2145</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="11" t="s">
-        <v>2277</v>
+        <v>2274</v>
       </c>
       <c r="B8" s="105" t="s">
         <v>1164</v>
@@ -20737,36 +21280,36 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="11" t="s">
+        <v>2107</v>
+      </c>
+      <c r="B9" s="103" t="s">
+        <v>2108</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>2109</v>
+      </c>
+      <c r="D9" s="103" t="s">
         <v>2110</v>
       </c>
-      <c r="B9" s="103" t="s">
+      <c r="E9" s="9" t="s">
         <v>2111</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>2112</v>
-      </c>
-      <c r="D9" s="103" t="s">
-        <v>2113</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>2114</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="11" t="s">
-        <v>2470</v>
+        <v>2465</v>
       </c>
       <c r="B10" s="103" t="s">
-        <v>2487</v>
+        <v>2482</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>2488</v>
+        <v>2483</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>2489</v>
+        <v>2484</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>2490</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -20869,13 +21412,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="11" t="s">
-        <v>2108</v>
+        <v>2105</v>
       </c>
       <c r="B17" s="103" t="s">
-        <v>2109</v>
+        <v>2106</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>2108</v>
+        <v>2105</v>
       </c>
       <c r="D17" s="103" t="s">
         <v>217</v>
@@ -20903,19 +21446,19 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="11" t="s">
+        <v>2100</v>
+      </c>
+      <c r="B19" s="103" t="s">
+        <v>2101</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>2102</v>
+      </c>
+      <c r="D19" s="103" t="s">
         <v>2103</v>
       </c>
-      <c r="B19" s="103" t="s">
+      <c r="E19" s="9" t="s">
         <v>2104</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>2105</v>
-      </c>
-      <c r="D19" s="103" t="s">
-        <v>2106</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>2107</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -21000,19 +21543,19 @@
       <c r="E24" s="7"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="159" t="s">
+      <c r="A25" s="95" t="s">
         <v>498</v>
       </c>
-      <c r="B25" s="158" t="s">
+      <c r="B25" s="151" t="s">
         <v>923</v>
       </c>
-      <c r="C25" s="160" t="s">
+      <c r="C25" s="152" t="s">
         <v>922</v>
       </c>
-      <c r="D25" s="161" t="s">
+      <c r="D25" s="153" t="s">
         <v>1006</v>
       </c>
-      <c r="E25" s="157" t="s">
+      <c r="E25" s="150" t="s">
         <v>1007</v>
       </c>
     </row>
@@ -21035,19 +21578,19 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="11" t="s">
+        <v>2095</v>
+      </c>
+      <c r="B27" s="103" t="s">
+        <v>2096</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>2097</v>
+      </c>
+      <c r="D27" s="103" t="s">
         <v>2098</v>
       </c>
-      <c r="B27" s="103" t="s">
+      <c r="E27" s="9" t="s">
         <v>2099</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>2100</v>
-      </c>
-      <c r="D27" s="103" t="s">
-        <v>2101</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>2102</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -21069,19 +21612,19 @@
     </row>
     <row r="29" spans="1:5" ht="24.75" customHeight="1">
       <c r="A29" s="11" t="s">
+        <v>2124</v>
+      </c>
+      <c r="B29" s="103" t="s">
+        <v>2125</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>2126</v>
+      </c>
+      <c r="D29" s="103" t="s">
         <v>2127</v>
       </c>
-      <c r="B29" s="103" t="s">
+      <c r="E29" s="9" t="s">
         <v>2128</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>2129</v>
-      </c>
-      <c r="D29" s="103" t="s">
-        <v>2130</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>2131</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -21112,10 +21655,10 @@
         <v>1702</v>
       </c>
       <c r="D31" s="101" t="s">
-        <v>2154</v>
+        <v>2151</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>2155</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -21137,13 +21680,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="11" t="s">
-        <v>2363</v>
+        <v>2360</v>
       </c>
       <c r="B33" s="105" t="s">
-        <v>2152</v>
+        <v>2149</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>2153</v>
+        <v>2150</v>
       </c>
       <c r="D33" s="105"/>
       <c r="E33" s="17"/>
@@ -21167,19 +21710,19 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="11" t="s">
+        <v>2208</v>
+      </c>
+      <c r="B35" s="103" t="s">
+        <v>2209</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>2210</v>
+      </c>
+      <c r="D35" s="103" t="s">
         <v>2211</v>
       </c>
-      <c r="B35" s="103" t="s">
+      <c r="E35" s="9" t="s">
         <v>2212</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>2213</v>
-      </c>
-      <c r="D35" s="103" t="s">
-        <v>2214</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>2215</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -21201,19 +21744,19 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B37" s="107" t="s">
+        <v>1938</v>
+      </c>
+      <c r="C37" s="18" t="s">
         <v>1937</v>
       </c>
-      <c r="B37" s="107" t="s">
+      <c r="D37" s="101" t="s">
         <v>1939</v>
       </c>
-      <c r="C37" s="18" t="s">
-        <v>1938</v>
-      </c>
-      <c r="D37" s="101" t="s">
+      <c r="E37" s="18" t="s">
         <v>1940</v>
-      </c>
-      <c r="E37" s="18" t="s">
-        <v>1941</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -21248,36 +21791,36 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="11" t="s">
-        <v>2460</v>
+        <v>2456</v>
       </c>
       <c r="B40" s="103" t="s">
-        <v>2471</v>
+        <v>2466</v>
       </c>
       <c r="C40" s="59" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="D40" s="103" t="s">
-        <v>2472</v>
+        <v>2467</v>
       </c>
       <c r="E40" s="59" t="s">
-        <v>2473</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="11" t="s">
+        <v>2137</v>
+      </c>
+      <c r="B41" s="103" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>2139</v>
+      </c>
+      <c r="D41" s="103" t="s">
         <v>2140</v>
       </c>
-      <c r="B41" s="103" t="s">
+      <c r="E41" s="9" t="s">
         <v>2141</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>2142</v>
-      </c>
-      <c r="D41" s="103" t="s">
-        <v>2143</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>2144</v>
       </c>
     </row>
   </sheetData>
@@ -21300,172 +21843,172 @@
   <sheetData>
     <row r="1" spans="1:5" ht="24">
       <c r="A1" s="46" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="B1" s="47" t="s">
+        <v>1895</v>
+      </c>
+      <c r="C1" s="38" t="s">
         <v>1896</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="D1" s="47" t="s">
         <v>1897</v>
       </c>
-      <c r="D1" s="47" t="s">
+      <c r="E1" s="38" t="s">
         <v>1898</v>
-      </c>
-      <c r="E1" s="38" t="s">
-        <v>1899</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18.75">
       <c r="A2" s="11" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="B2" s="21" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>1900</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="103" t="s">
         <v>1901</v>
       </c>
-      <c r="D2" s="103" t="s">
+      <c r="E2" s="9" t="s">
         <v>1902</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>1903</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="37.5">
       <c r="A3" s="11" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="B3" s="21" t="s">
+        <v>1903</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>1904</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="103" t="s">
         <v>1905</v>
       </c>
-      <c r="D3" s="103" t="s">
+      <c r="E3" s="9" t="s">
         <v>1906</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>1907</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="37.5">
       <c r="A4" s="11" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="B4" s="21" t="s">
+        <v>1923</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>1924</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="D4" s="103" t="s">
         <v>1925</v>
       </c>
-      <c r="D4" s="103" t="s">
+      <c r="E4" s="9" t="s">
         <v>1926</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>1927</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="37.5">
       <c r="A5" s="11" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="B5" s="21" t="s">
+        <v>1907</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>1908</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="D5" s="103" t="s">
         <v>1909</v>
       </c>
-      <c r="D5" s="103" t="s">
+      <c r="E5" s="9" t="s">
         <v>1910</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>1911</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="37.5">
       <c r="A6" s="11" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="B6" s="21" t="s">
+        <v>1915</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>1916</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="D6" s="103" t="s">
         <v>1917</v>
       </c>
-      <c r="D6" s="103" t="s">
+      <c r="E6" s="9" t="s">
         <v>1918</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>1919</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="37.5">
       <c r="A7" s="11" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="B7" s="21" t="s">
+        <v>1927</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>1928</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="D7" s="103" t="s">
         <v>1929</v>
       </c>
-      <c r="D7" s="103" t="s">
+      <c r="E7" s="9" t="s">
         <v>1930</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>1931</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="37.5">
       <c r="A8" s="11" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="B8" s="21" t="s">
+        <v>1911</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>1912</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="D8" s="103" t="s">
         <v>1913</v>
       </c>
-      <c r="D8" s="103" t="s">
+      <c r="E8" s="9" t="s">
         <v>1914</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>1915</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="37.5">
       <c r="A9" s="11" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="B9" s="21" t="s">
+        <v>1919</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>1920</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="D9" s="103" t="s">
         <v>1921</v>
       </c>
-      <c r="D9" s="103" t="s">
+      <c r="E9" s="9" t="s">
         <v>1922</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>1923</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="37.5">
       <c r="A10" s="11" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="B10" s="21" t="s">
+        <v>1931</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>1932</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="D10" s="103" t="s">
         <v>1933</v>
       </c>
-      <c r="D10" s="103" t="s">
+      <c r="E10" s="9" t="s">
         <v>1934</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>1935</v>
       </c>
     </row>
   </sheetData>
